--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06475</v>
+        <v>0.0356</v>
       </c>
       <c r="E2">
-        <v>0.0591</v>
+        <v>0.155</v>
       </c>
       <c r="F2">
-        <v>0.405</v>
+        <v>0.1155</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2.546485424807065e-06</v>
+        <v>2.601161226806696e-06</v>
       </c>
       <c r="J2">
-        <v>2.167751788939098e-06</v>
+        <v>2.064207250251094e-06</v>
       </c>
       <c r="K2">
-        <v>36435.73</v>
+        <v>31670.8</v>
       </c>
       <c r="L2">
-        <v>0.2701788847215363</v>
+        <v>0.2572287409917391</v>
       </c>
       <c r="M2">
-        <v>7810.0058</v>
+        <v>10682.9805</v>
       </c>
       <c r="N2">
-        <v>0.02876712093637093</v>
+        <v>0.04298119574283012</v>
       </c>
       <c r="O2">
-        <v>0.2143501941638057</v>
+        <v>0.3373132506914888</v>
       </c>
       <c r="P2">
-        <v>7793.0888</v>
+        <v>9928.1805</v>
       </c>
       <c r="Q2">
-        <v>0.02870480940967775</v>
+        <v>0.03994438344623479</v>
       </c>
       <c r="R2">
-        <v>0.2138858971674233</v>
+        <v>0.3134805720095483</v>
       </c>
       <c r="S2">
-        <v>16.91700000000001</v>
+        <v>754.8000000000001</v>
       </c>
       <c r="T2">
-        <v>0.002166067533522192</v>
+        <v>0.07065443955457935</v>
       </c>
       <c r="U2">
-        <v>1045425.7</v>
+        <v>945555.6</v>
       </c>
       <c r="V2">
-        <v>3.850686966441208</v>
+        <v>3.804285735551907</v>
       </c>
       <c r="W2">
-        <v>0.0902280457066896</v>
+        <v>0.07092869934222655</v>
       </c>
       <c r="X2">
-        <v>0.1115184633036762</v>
+        <v>0.199497312647869</v>
       </c>
       <c r="Y2">
-        <v>-0.02129041759698655</v>
+        <v>-0.1285686133056425</v>
       </c>
       <c r="Z2">
-        <v>0.07992008203089523</v>
+        <v>0.0923625877110496</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04693811552980082</v>
+        <v>0.07099752179897709</v>
       </c>
       <c r="AC2">
-        <v>-0.04693811552980082</v>
+        <v>-0.07099752179897709</v>
       </c>
       <c r="AD2">
-        <v>1884790.9</v>
+        <v>2218220.4</v>
       </c>
       <c r="AE2">
-        <v>1.877932889392269</v>
+        <v>1.423684830778782</v>
       </c>
       <c r="AF2">
-        <v>1884792.77793289</v>
+        <v>2218221.823684831</v>
       </c>
       <c r="AG2">
-        <v>839367.0779328896</v>
+        <v>1272666.223684831</v>
       </c>
       <c r="AH2">
-        <v>0.8740932243935463</v>
+        <v>0.899240745521086</v>
       </c>
       <c r="AI2">
-        <v>0.792677193942702</v>
+        <v>0.8429959603016021</v>
       </c>
       <c r="AJ2">
-        <v>0.7556026474377339</v>
+        <v>0.8366109434074839</v>
       </c>
       <c r="AK2">
-        <v>0.6299993461343812</v>
+        <v>0.7549332707187522</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>2621405.980528512</v>
+        <v>3666480</v>
       </c>
       <c r="AP2">
-        <v>1167409.009642406</v>
+        <v>2103580.535016249</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
+          <t>Close Brothers Group plc (LSE:CBG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00528</v>
+        <v>0.0356</v>
       </c>
       <c r="E3">
-        <v>0.357</v>
+        <v>-0.0288</v>
       </c>
       <c r="F3">
-        <v>0.483</v>
+        <v>0.09</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,85 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>8203.6</v>
+        <v>201</v>
       </c>
       <c r="L3">
-        <v>0.3790382198565831</v>
+        <v>0.1825944767441861</v>
       </c>
       <c r="M3">
-        <v>1136.2272</v>
+        <v>127.8</v>
       </c>
       <c r="N3">
-        <v>0.02472031381558765</v>
+        <v>0.06800766283524903</v>
       </c>
       <c r="O3">
-        <v>0.1385034862743186</v>
+        <v>0.6358208955223881</v>
       </c>
       <c r="P3">
-        <v>1136.2272</v>
+        <v>116.2</v>
       </c>
       <c r="Q3">
-        <v>0.02472031381558765</v>
+        <v>0.0618348233290762</v>
       </c>
       <c r="R3">
-        <v>0.1385034862743186</v>
+        <v>0.5781094527363184</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>11.59999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.09076682316118932</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1682.7</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.895434227330779</v>
       </c>
       <c r="W3">
-        <v>0.1286784716568867</v>
+        <v>0.09204561066080506</v>
       </c>
       <c r="X3">
-        <v>0.04621578350715233</v>
+        <v>0.1138694181394443</v>
       </c>
       <c r="Y3">
-        <v>0.08246268814973437</v>
+        <v>-0.02182380747863923</v>
       </c>
       <c r="Z3">
-        <v>0.3394867982061937</v>
+        <v>0.2974813533672035</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04340776592568363</v>
+        <v>0.06597280318096302</v>
       </c>
       <c r="AC3">
-        <v>-0.04340776592568363</v>
+        <v>-0.06597280318096302</v>
       </c>
       <c r="AD3">
-        <v>8236</v>
+        <v>3600.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8236</v>
+        <v>3600.7</v>
       </c>
       <c r="AG3">
-        <v>8236</v>
+        <v>1918</v>
       </c>
       <c r="AH3">
-        <v>0.1519576821102855</v>
+        <v>0.6570740341977044</v>
       </c>
       <c r="AI3">
-        <v>0.103918127253021</v>
+        <v>0.640990493822765</v>
       </c>
       <c r="AJ3">
-        <v>0.1519576821102855</v>
+        <v>0.5051090277046244</v>
       </c>
       <c r="AK3">
-        <v>0.103918127253021</v>
+        <v>0.4874577477317203</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Close Brothers Group plc (LSE:CBG)</t>
+          <t>Bank of Georgia Group PLC (LSE:BGEO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06860000000000001</v>
+        <v>0.236</v>
       </c>
       <c r="E4">
-        <v>0.0162</v>
+        <v>0.195</v>
       </c>
       <c r="F4">
-        <v>0.05</v>
+        <v>0.141</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,97 +859,103 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.000506905719918081</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.0004587335330315984</v>
       </c>
       <c r="K4">
-        <v>281</v>
+        <v>353.7</v>
       </c>
       <c r="L4">
-        <v>0.216737369841882</v>
+        <v>0.5598290598290598</v>
       </c>
       <c r="M4">
-        <v>137.2</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="N4">
-        <v>0.04845317135188586</v>
+        <v>0.04687832187655021</v>
       </c>
       <c r="O4">
-        <v>0.4882562277580072</v>
+        <v>0.1870229007633588</v>
       </c>
       <c r="P4">
-        <v>120.4</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.04252012996185902</v>
+        <v>0.04687832187655021</v>
       </c>
       <c r="R4">
-        <v>0.4284697508896798</v>
+        <v>0.1870229007633588</v>
       </c>
       <c r="S4">
-        <v>16.80000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.1224489795918368</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1997.7</v>
+        <v>978.1</v>
       </c>
       <c r="V4">
-        <v>0.7055021895747987</v>
+        <v>0.6931471901353554</v>
       </c>
       <c r="W4">
-        <v>0.1474369064483971</v>
+        <v>0.3815945625202287</v>
       </c>
       <c r="X4">
-        <v>0.07061535544501919</v>
+        <v>0.1031988650624544</v>
       </c>
       <c r="Y4">
-        <v>0.07682155100337788</v>
+        <v>0.2783956974577743</v>
       </c>
       <c r="Z4">
-        <v>0.3925100663013532</v>
+        <v>0.2719965377165626</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.0001247739327190812</v>
       </c>
       <c r="AB4">
-        <v>0.04385572439387023</v>
+        <v>0.06975128295143913</v>
       </c>
       <c r="AC4">
-        <v>-0.04385572439387023</v>
+        <v>-0.06962650901872006</v>
       </c>
       <c r="AD4">
-        <v>3646.5</v>
+        <v>2050.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.423684830778782</v>
       </c>
       <c r="AF4">
-        <v>3646.5</v>
+        <v>2052.023684830779</v>
       </c>
       <c r="AG4">
-        <v>1648.8</v>
+        <v>1073.923684830779</v>
       </c>
       <c r="AH4">
-        <v>0.5628965283030518</v>
+        <v>0.5925354886454333</v>
       </c>
       <c r="AI4">
-        <v>0.6256004666483667</v>
+        <v>0.6168673002955534</v>
       </c>
       <c r="AJ4">
-        <v>0.3680028568877779</v>
+        <v>0.4321583296715778</v>
       </c>
       <c r="AK4">
-        <v>0.4303724778784161</v>
+        <v>0.457295543290419</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>3389.421487603306</v>
+      </c>
+      <c r="AP4">
+        <v>1775.080470794676</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Georgia Group PLC (LSE:BGEO)</t>
+          <t>Secure Trust Bank PLC (LSE:STB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,10 +975,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0837</v>
+        <v>0.124</v>
       </c>
       <c r="E5">
-        <v>0.102</v>
+        <v>0.146</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.0008731589680181699</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.0007937124211221657</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>209.8</v>
+        <v>47</v>
       </c>
       <c r="L5">
-        <v>0.5334350368675311</v>
+        <v>0.2547425474254743</v>
       </c>
       <c r="M5">
-        <v>22.278</v>
+        <v>13.9</v>
       </c>
       <c r="N5">
-        <v>0.02100113122171946</v>
+        <v>0.08229721728833629</v>
       </c>
       <c r="O5">
-        <v>0.106186844613918</v>
+        <v>0.2957446808510638</v>
       </c>
       <c r="P5">
-        <v>22.278</v>
+        <v>13.9</v>
       </c>
       <c r="Q5">
-        <v>0.02100113122171946</v>
+        <v>0.08229721728833629</v>
       </c>
       <c r="R5">
-        <v>0.106186844613918</v>
+        <v>0.2957446808510638</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,67 +1023,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>408</v>
+        <v>415.7</v>
       </c>
       <c r="V5">
-        <v>0.3846153846153846</v>
+        <v>2.461219656601539</v>
       </c>
       <c r="W5">
-        <v>0.2922005571030641</v>
+        <v>0.1178831201404565</v>
       </c>
       <c r="X5">
-        <v>0.07993099062491486</v>
+        <v>0.1453803668010036</v>
       </c>
       <c r="Y5">
-        <v>0.2122695664781492</v>
+        <v>-0.02749724666054715</v>
       </c>
       <c r="Z5">
-        <v>0.2283073304017603</v>
+        <v>0.2803951367781155</v>
       </c>
       <c r="AA5">
-        <v>0.0001812103639731194</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04404772438002267</v>
+        <v>0.06979470656978146</v>
       </c>
       <c r="AC5">
-        <v>-0.04386651401604955</v>
+        <v>-0.06979470656978146</v>
       </c>
       <c r="AD5">
-        <v>1813.2</v>
+        <v>554</v>
       </c>
       <c r="AE5">
-        <v>1.877932889392269</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1815.077932889392</v>
+        <v>554</v>
       </c>
       <c r="AG5">
-        <v>1407.077932889392</v>
+        <v>138.3</v>
       </c>
       <c r="AH5">
-        <v>0.6311387253720414</v>
+        <v>0.7663577258265321</v>
       </c>
       <c r="AI5">
-        <v>0.6609469514525074</v>
+        <v>0.5918803418803419</v>
       </c>
       <c r="AJ5">
-        <v>0.5701570220055353</v>
+        <v>0.4501953124999999</v>
       </c>
       <c r="AK5">
-        <v>0.6017839417167891</v>
+        <v>0.2658081875840861</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>2521.835883171071</v>
-      </c>
-      <c r="AP5">
-        <v>1956.992952558265</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arbuthnot Banking Group PLC (AIM:ARBB)</t>
+          <t>HSBC Holdings plc (LSE:HSBA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,10 +1097,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.155</v>
+        <v>-0.00138</v>
       </c>
       <c r="E6">
-        <v>-0.5660000000000001</v>
+        <v>0.152</v>
+      </c>
+      <c r="F6">
+        <v>0.183</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,85 +1118,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3.63</v>
+        <v>13221</v>
       </c>
       <c r="L6">
-        <v>0.03389355742296919</v>
+        <v>0.2860078743564228</v>
       </c>
       <c r="M6">
-        <v>3.432</v>
+        <v>5328.504000000001</v>
       </c>
       <c r="N6">
-        <v>0.02020011771630371</v>
+        <v>0.04345283635862488</v>
       </c>
       <c r="O6">
-        <v>0.9454545454545454</v>
+        <v>0.4030333560245065</v>
       </c>
       <c r="P6">
-        <v>3.315</v>
+        <v>5328.504000000001</v>
       </c>
       <c r="Q6">
-        <v>0.01951147733961154</v>
+        <v>0.04345283635862488</v>
       </c>
       <c r="R6">
-        <v>0.9132231404958678</v>
+        <v>0.4030333560245065</v>
       </c>
       <c r="S6">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.03409090909090909</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>995.7</v>
+        <v>309505</v>
       </c>
       <c r="V6">
-        <v>5.860506180105944</v>
+        <v>2.52394858241191</v>
       </c>
       <c r="W6">
-        <v>0.01522651006711409</v>
+        <v>0.07523473510499061</v>
       </c>
       <c r="X6">
-        <v>0.05198772329634922</v>
+        <v>0.199497312647869</v>
       </c>
       <c r="Y6">
-        <v>-0.03676121322923513</v>
+        <v>-0.1242625775428784</v>
       </c>
       <c r="Z6">
-        <v>-0.2938271604938271</v>
+        <v>0.1328161588300363</v>
       </c>
       <c r="AA6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0442791392818349</v>
+        <v>0.0698153519975879</v>
       </c>
       <c r="AC6">
-        <v>-0.0442791392818349</v>
+        <v>-0.0698153519975879</v>
       </c>
       <c r="AD6">
-        <v>75</v>
+        <v>689475</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>75</v>
+        <v>689475</v>
       </c>
       <c r="AG6">
-        <v>-920.7</v>
+        <v>379970</v>
       </c>
       <c r="AH6">
-        <v>0.3062474479379338</v>
+        <v>0.8490001813810895</v>
       </c>
       <c r="AI6">
-        <v>0.214041095890411</v>
+        <v>0.7875502017206797</v>
       </c>
       <c r="AJ6">
-        <v>1.226291955247736</v>
+        <v>0.7560128158269056</v>
       </c>
       <c r="AK6">
-        <v>1.426778242677824</v>
+        <v>0.6713689764171863</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1210,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Secure Trust Bank PLC (LSE:STB)</t>
+          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,10 +1222,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.112</v>
+        <v>-0.017</v>
       </c>
       <c r="E7">
-        <v>-0.234</v>
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.0374</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,28 +1243,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>52.9</v>
+        <v>4856.1</v>
       </c>
       <c r="L7">
-        <v>0.2662304982385506</v>
+        <v>0.2689957734854066</v>
       </c>
       <c r="M7">
-        <v>11.3</v>
+        <v>1536.8117</v>
       </c>
       <c r="N7">
-        <v>0.03365098272781417</v>
+        <v>0.04203671072354671</v>
       </c>
       <c r="O7">
-        <v>0.2136105860113422</v>
+        <v>0.3164703568707398</v>
       </c>
       <c r="P7">
-        <v>11.3</v>
+        <v>1536.8117</v>
       </c>
       <c r="Q7">
-        <v>0.03365098272781417</v>
+        <v>0.04203671072354671</v>
       </c>
       <c r="R7">
-        <v>0.2136105860113422</v>
+        <v>0.3164703568707398</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1267,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>250.9</v>
+        <v>94537.7</v>
       </c>
       <c r="V7">
-        <v>0.747170935080405</v>
+        <v>2.58590818079368</v>
       </c>
       <c r="W7">
-        <v>0.1647461849891</v>
+        <v>0.06863871703649679</v>
       </c>
       <c r="X7">
-        <v>0.07571203221995829</v>
+        <v>0.184415680851683</v>
       </c>
       <c r="Y7">
-        <v>0.08903415276914167</v>
+        <v>-0.1157769638151862</v>
       </c>
       <c r="Z7">
-        <v>0.3610101744186046</v>
+        <v>0.2285594551856246</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04622451949756654</v>
+        <v>0.07099752179897709</v>
       </c>
       <c r="AC7">
-        <v>-0.04622451949756654</v>
+        <v>-0.07099752179897709</v>
       </c>
       <c r="AD7">
-        <v>510.2</v>
+        <v>181686.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>510.2</v>
+        <v>181686.6</v>
       </c>
       <c r="AG7">
-        <v>259.3</v>
+        <v>87148.90000000001</v>
       </c>
       <c r="AH7">
-        <v>0.6030732860520095</v>
+        <v>0.8324876492242218</v>
       </c>
       <c r="AI7">
-        <v>0.5613378809550006</v>
+        <v>0.778568878859546</v>
       </c>
       <c r="AJ7">
-        <v>0.4357250882204671</v>
+        <v>0.704474337490714</v>
       </c>
       <c r="AK7">
-        <v>0.3940729483282674</v>
+        <v>0.6277744161588221</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1332,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc (LSE:HSBA)</t>
+          <t>Standard Chartered PLC (LSE:STAN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1341,13 +1347,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0144</v>
+        <v>0.0307</v>
       </c>
       <c r="E8">
-        <v>0.188</v>
+        <v>0.158</v>
       </c>
       <c r="F8">
-        <v>0.635</v>
+        <v>0.334</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1362,28 +1368,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>12747</v>
+        <v>2814</v>
       </c>
       <c r="L8">
-        <v>0.2573903561909378</v>
+        <v>0.1892909995963944</v>
       </c>
       <c r="M8">
-        <v>4425.124</v>
+        <v>376.74</v>
       </c>
       <c r="N8">
-        <v>0.03621409994320479</v>
+        <v>0.01733484868702578</v>
       </c>
       <c r="O8">
-        <v>0.3471502314270024</v>
+        <v>0.1338805970149254</v>
       </c>
       <c r="P8">
-        <v>4425.124</v>
+        <v>376.74</v>
       </c>
       <c r="Q8">
-        <v>0.03621409994320479</v>
+        <v>0.01733484868702578</v>
       </c>
       <c r="R8">
-        <v>0.3471502314270024</v>
+        <v>0.1338805970149254</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1392,55 +1398,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>409918</v>
+        <v>66521</v>
       </c>
       <c r="V8">
-        <v>3.354665636605578</v>
+        <v>3.060815070100446</v>
       </c>
       <c r="W8">
-        <v>0.06642383691845923</v>
+        <v>0.0547194026367985</v>
       </c>
       <c r="X8">
-        <v>0.1431059359824374</v>
+        <v>0.2617662726074869</v>
       </c>
       <c r="Y8">
-        <v>-0.0766820990639782</v>
+        <v>-0.2070468699706884</v>
       </c>
       <c r="Z8">
-        <v>0.08698431879496403</v>
+        <v>0.07928660191896404</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0476517115620351</v>
+        <v>0.07109833172370217</v>
       </c>
       <c r="AC8">
-        <v>-0.0476517115620351</v>
+        <v>-0.07109833172370217</v>
       </c>
       <c r="AD8">
-        <v>559819</v>
+        <v>180773</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>559819</v>
+        <v>180773</v>
       </c>
       <c r="AG8">
-        <v>149901</v>
+        <v>114252</v>
       </c>
       <c r="AH8">
-        <v>0.8208340493515953</v>
+        <v>0.8926792822537197</v>
       </c>
       <c r="AI8">
-        <v>0.7303498463160202</v>
+        <v>0.7833266890837869</v>
       </c>
       <c r="AJ8">
-        <v>0.5509154175903657</v>
+        <v>0.8401802844576354</v>
       </c>
       <c r="AK8">
-        <v>0.4203735382371911</v>
+        <v>0.6955769991781072</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1457,7 +1463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standard Chartered PLC (LSE:STAN)</t>
+          <t>NatWest Group plc (LSE:NWG)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,10 +1472,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0609</v>
+        <v>-0.0104</v>
       </c>
       <c r="F9">
-        <v>0.298</v>
+        <v>0.31</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,28 +1490,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>2199</v>
+        <v>3078.8</v>
       </c>
       <c r="L9">
-        <v>0.1558800595449068</v>
+        <v>0.2217676294748974</v>
       </c>
       <c r="M9">
-        <v>369.48</v>
+        <v>1245.7788</v>
       </c>
       <c r="N9">
-        <v>0.01976389030045949</v>
+        <v>0.04037107802788238</v>
       </c>
       <c r="O9">
-        <v>0.1680218281036835</v>
+        <v>0.4046312849162011</v>
       </c>
       <c r="P9">
-        <v>369.48</v>
+        <v>1245.7788</v>
       </c>
       <c r="Q9">
-        <v>0.01976389030045949</v>
+        <v>0.04037107802788238</v>
       </c>
       <c r="R9">
-        <v>0.1680218281036835</v>
+        <v>0.4046312849162011</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,55 +1520,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>75617</v>
+        <v>183657.8</v>
       </c>
       <c r="V9">
-        <v>4.04483623700835</v>
+        <v>5.951669248368343</v>
       </c>
       <c r="W9">
-        <v>0.04509196792913241</v>
+        <v>0.05510403150029084</v>
       </c>
       <c r="X9">
-        <v>0.2897340595358647</v>
+        <v>0.2268101069479499</v>
       </c>
       <c r="Y9">
-        <v>-0.2446420916067323</v>
+        <v>-0.1717060754476591</v>
       </c>
       <c r="Z9">
-        <v>0.07410929111024722</v>
+        <v>0.4496824075483673</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04913570853796134</v>
+        <v>0.07230590482702791</v>
       </c>
       <c r="AC9">
-        <v>-0.04913570853796134</v>
+        <v>-0.07230590482702791</v>
       </c>
       <c r="AD9">
-        <v>210194</v>
+        <v>209983</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>210194</v>
+        <v>209983</v>
       </c>
       <c r="AG9">
-        <v>134577</v>
+        <v>26325.20000000001</v>
       </c>
       <c r="AH9">
-        <v>0.9183240588111165</v>
+        <v>0.8718732509221844</v>
       </c>
       <c r="AI9">
-        <v>0.7976124069836716</v>
+        <v>0.8435281291200646</v>
       </c>
       <c r="AJ9">
-        <v>0.8780290164459583</v>
+        <v>0.4603643714784362</v>
       </c>
       <c r="AK9">
-        <v>0.7161703350504491</v>
+        <v>0.4032881715290673</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1579,7 +1585,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NatWest Group plc (LSE:NWG)</t>
+          <t>Barclays PLC (LSE:BARC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,10 +1594,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.00635</v>
+        <v>0.04389999999999999</v>
+      </c>
+      <c r="E10">
+        <v>1.442</v>
       </c>
       <c r="F10">
-        <v>0.9790000000000001</v>
+        <v>0.00148</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1606,28 +1615,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3713</v>
+        <v>6578.8</v>
       </c>
       <c r="L10">
-        <v>0.2361959287531807</v>
+        <v>0.2499154766924605</v>
       </c>
       <c r="M10">
-        <v>912.7323</v>
+        <v>1110.396</v>
       </c>
       <c r="N10">
-        <v>0.02650433108478937</v>
+        <v>0.03664939368535009</v>
       </c>
       <c r="O10">
-        <v>0.2458207110153515</v>
+        <v>0.1687839727609898</v>
       </c>
       <c r="P10">
-        <v>912.7323</v>
+        <v>1110.396</v>
       </c>
       <c r="Q10">
-        <v>0.02650433108478937</v>
+        <v>0.03664939368535009</v>
       </c>
       <c r="R10">
-        <v>0.2458207110153515</v>
+        <v>0.1687839727609898</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1636,55 +1645,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>235066.5</v>
+        <v>286451.3</v>
       </c>
       <c r="V10">
-        <v>6.825966762590346</v>
+        <v>9.454524750972018</v>
       </c>
       <c r="W10">
-        <v>0.06725218755263983</v>
+        <v>0.07092869934222655</v>
       </c>
       <c r="X10">
-        <v>0.1761029996986813</v>
+        <v>0.7792631096858946</v>
       </c>
       <c r="Y10">
-        <v>-0.1088508121460415</v>
+        <v>-0.7083344103436681</v>
       </c>
       <c r="Z10">
-        <v>0.08396206965433477</v>
+        <v>0.04002575116040634</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05001965293892135</v>
+        <v>0.07260534356306238</v>
       </c>
       <c r="AC10">
-        <v>-0.05001965293892135</v>
+        <v>-0.07260534356306238</v>
       </c>
       <c r="AD10">
-        <v>209399.9</v>
+        <v>930686.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>209399.9</v>
+        <v>930686.5</v>
       </c>
       <c r="AG10">
-        <v>-25666.60000000001</v>
+        <v>644235.2</v>
       </c>
       <c r="AH10">
-        <v>0.8587699979904608</v>
+        <v>0.9684721175985913</v>
       </c>
       <c r="AI10">
-        <v>0.7873529399599856</v>
+        <v>0.9247112011603421</v>
       </c>
       <c r="AJ10">
-        <v>-2.926469414514569</v>
+        <v>0.955083294664605</v>
       </c>
       <c r="AK10">
-        <v>-0.830962386443839</v>
+        <v>0.8947580625560321</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1701,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Barclays PLC (LSE:BARC)</t>
+          <t>Virgin Money UK PLC (LSE:VMUK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1710,10 +1719,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0429</v>
+        <v>0.11</v>
+      </c>
+      <c r="E11">
+        <v>0.262</v>
       </c>
       <c r="F11">
-        <v>0.405</v>
+        <v>-0.0387</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1728,212 +1740,90 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>8492.5</v>
+        <v>520.4</v>
       </c>
       <c r="L11">
-        <v>0.2861286964256234</v>
+        <v>0.2806601229640815</v>
       </c>
       <c r="M11">
-        <v>685.5323</v>
+        <v>876.9000000000001</v>
       </c>
       <c r="N11">
-        <v>0.01619215915988974</v>
+        <v>0.2907782604370462</v>
       </c>
       <c r="O11">
-        <v>0.08072208419193405</v>
+        <v>1.685049961568025</v>
       </c>
       <c r="P11">
-        <v>685.5323</v>
+        <v>133.7</v>
       </c>
       <c r="Q11">
-        <v>0.01619215915988974</v>
+        <v>0.04433464867195012</v>
       </c>
       <c r="R11">
-        <v>0.08072208419193405</v>
+        <v>0.2569177555726364</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>743.2</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.8475310753791766</v>
       </c>
       <c r="U11">
-        <v>307353</v>
+        <v>1806.3</v>
       </c>
       <c r="V11">
-        <v>7.259626853861724</v>
+        <v>0.5989654143316643</v>
       </c>
       <c r="W11">
-        <v>0.09683922692820385</v>
+        <v>0.07042425062588809</v>
       </c>
       <c r="X11">
-        <v>0.4957324946785557</v>
+        <v>0.2183055593235964</v>
       </c>
       <c r="Y11">
-        <v>-0.3988932677503519</v>
+        <v>-0.1478813086977083</v>
       </c>
       <c r="Z11">
-        <v>0.04504559468875184</v>
+        <v>0.07964468727583557</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05087618491154079</v>
+        <v>0.07364945548960727</v>
       </c>
       <c r="AC11">
-        <v>-0.05087618491154079</v>
+        <v>-0.07364945548960727</v>
       </c>
       <c r="AD11">
-        <v>872279.8</v>
+        <v>19411</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>872279.8</v>
+        <v>19411</v>
       </c>
       <c r="AG11">
-        <v>564926.8</v>
+        <v>17604.7</v>
       </c>
       <c r="AH11">
-        <v>0.9537103559511406</v>
+        <v>0.8655308181765484</v>
       </c>
       <c r="AI11">
-        <v>0.9025432484259449</v>
+        <v>0.7331656317514995</v>
       </c>
       <c r="AJ11">
-        <v>0.9302818987652982</v>
+        <v>0.8537516246047603</v>
       </c>
       <c r="AK11">
-        <v>0.857098078531584</v>
+        <v>0.7136278694571795</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Virgin Money UK PLC (LSE:VMUK)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.111</v>
-      </c>
-      <c r="F12">
-        <v>-0.08689999999999999</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>533.3</v>
-      </c>
-      <c r="L12">
-        <v>0.2438165775156585</v>
-      </c>
-      <c r="M12">
-        <v>106.7</v>
-      </c>
-      <c r="N12">
-        <v>0.03077766239760009</v>
-      </c>
-      <c r="O12">
-        <v>0.200075004687793</v>
-      </c>
-      <c r="P12">
-        <v>106.7</v>
-      </c>
-      <c r="Q12">
-        <v>0.03077766239760009</v>
-      </c>
-      <c r="R12">
-        <v>0.200075004687793</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>13818.9</v>
-      </c>
-      <c r="V12">
-        <v>3.986067843544479</v>
-      </c>
-      <c r="W12">
-        <v>0.08361686448517537</v>
-      </c>
-      <c r="X12">
-        <v>0.1617355314811667</v>
-      </c>
-      <c r="Y12">
-        <v>-0.07811866699599131</v>
-      </c>
-      <c r="Z12">
-        <v>0.17339019730636</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.05097734284854803</v>
-      </c>
-      <c r="AC12">
-        <v>-0.05097734284854803</v>
-      </c>
-      <c r="AD12">
-        <v>18817.3</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>18817.3</v>
-      </c>
-      <c r="AG12">
-        <v>4998.4</v>
-      </c>
-      <c r="AH12">
-        <v>0.8444271924825324</v>
-      </c>
-      <c r="AI12">
-        <v>0.7180311980096769</v>
-      </c>
-      <c r="AJ12">
-        <v>0.5904644899116381</v>
-      </c>
-      <c r="AK12">
-        <v>0.4034905028293738</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0356</v>
+        <v>0.0364</v>
       </c>
       <c r="E2">
-        <v>0.155</v>
+        <v>0.1395</v>
       </c>
       <c r="F2">
-        <v>0.1155</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2.601161226806696e-06</v>
+        <v>2.610720697709334e-06</v>
       </c>
       <c r="J2">
-        <v>2.064207250251094e-06</v>
+        <v>1.962337555980011e-06</v>
       </c>
       <c r="K2">
-        <v>31670.8</v>
+        <v>53766.8</v>
       </c>
       <c r="L2">
-        <v>0.2572287409917391</v>
+        <v>0.3409686444912879</v>
       </c>
       <c r="M2">
-        <v>10682.9805</v>
+        <v>16458.9091</v>
       </c>
       <c r="N2">
-        <v>0.04298119574283012</v>
+        <v>0.05978223115100409</v>
       </c>
       <c r="O2">
-        <v>0.3373132506914888</v>
+        <v>0.3061165830958882</v>
       </c>
       <c r="P2">
-        <v>9928.1805</v>
+        <v>16095.4981</v>
       </c>
       <c r="Q2">
-        <v>0.03994438344623479</v>
+        <v>0.0584622457089059</v>
       </c>
       <c r="R2">
-        <v>0.3134805720095483</v>
+        <v>0.2993575607996013</v>
       </c>
       <c r="S2">
-        <v>754.8000000000001</v>
+        <v>363.4110000000001</v>
       </c>
       <c r="T2">
-        <v>0.07065443955457935</v>
+        <v>0.02207989592700284</v>
       </c>
       <c r="U2">
-        <v>945555.6</v>
+        <v>977576.9</v>
       </c>
       <c r="V2">
-        <v>3.804285735551907</v>
+        <v>3.550765597440598</v>
       </c>
       <c r="W2">
-        <v>0.07092869934222655</v>
+        <v>0.1057346158737809</v>
       </c>
       <c r="X2">
-        <v>0.199497312647869</v>
+        <v>0.1435729716997858</v>
       </c>
       <c r="Y2">
-        <v>-0.1285686133056425</v>
+        <v>-0.03783835582600489</v>
       </c>
       <c r="Z2">
-        <v>0.0923625877110496</v>
+        <v>0.09411516775476092</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07099752179897709</v>
+        <v>0.06021282006873493</v>
       </c>
       <c r="AC2">
-        <v>-0.07099752179897709</v>
+        <v>-0.06021282006873493</v>
       </c>
       <c r="AD2">
-        <v>2218220.4</v>
+        <v>2185153.9</v>
       </c>
       <c r="AE2">
-        <v>1.423684830778782</v>
+        <v>1.586598151656657</v>
       </c>
       <c r="AF2">
-        <v>2218221.823684831</v>
+        <v>2185155.486598152</v>
       </c>
       <c r="AG2">
-        <v>1272666.223684831</v>
+        <v>1207578.586598152</v>
       </c>
       <c r="AH2">
-        <v>0.899240745521086</v>
+        <v>0.888104950400084</v>
       </c>
       <c r="AI2">
-        <v>0.8429959603016021</v>
+        <v>0.8350388304744233</v>
       </c>
       <c r="AJ2">
-        <v>0.8366109434074839</v>
+        <v>0.8143396708405857</v>
       </c>
       <c r="AK2">
-        <v>0.7549332707187522</v>
+        <v>0.7366634596008048</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>3666480</v>
+        <v>2997467.626886145</v>
       </c>
       <c r="AP2">
-        <v>2103580.535016249</v>
+        <v>1656486.401369207</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0356</v>
+        <v>0.00052</v>
       </c>
       <c r="E3">
-        <v>-0.0288</v>
-      </c>
-      <c r="F3">
-        <v>0.09</v>
+        <v>-0.167</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,85 +737,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>201</v>
+        <v>104.3</v>
       </c>
       <c r="L3">
-        <v>0.1825944767441861</v>
+        <v>0.1005688940314338</v>
       </c>
       <c r="M3">
-        <v>127.8</v>
+        <v>133.93</v>
       </c>
       <c r="N3">
-        <v>0.06800766283524903</v>
+        <v>0.08888372710379613</v>
       </c>
       <c r="O3">
-        <v>0.6358208955223881</v>
+        <v>1.284084372003835</v>
       </c>
       <c r="P3">
-        <v>116.2</v>
+        <v>127.5</v>
       </c>
       <c r="Q3">
-        <v>0.0618348233290762</v>
+        <v>0.08461640562782055</v>
       </c>
       <c r="R3">
-        <v>0.5781094527363184</v>
+        <v>1.222435282837967</v>
       </c>
       <c r="S3">
-        <v>11.59999999999999</v>
+        <v>6.430000000000007</v>
       </c>
       <c r="T3">
-        <v>0.09076682316118932</v>
+        <v>0.04801015455835143</v>
       </c>
       <c r="U3">
-        <v>1682.7</v>
+        <v>2841.7</v>
       </c>
       <c r="V3">
-        <v>0.895434227330779</v>
+        <v>1.885917175471197</v>
       </c>
       <c r="W3">
-        <v>0.09204561066080506</v>
+        <v>0.05171815341895175</v>
       </c>
       <c r="X3">
-        <v>0.1138694181394443</v>
+        <v>0.1023164514801041</v>
       </c>
       <c r="Y3">
-        <v>-0.02182380747863923</v>
+        <v>-0.05059829806115237</v>
       </c>
       <c r="Z3">
-        <v>0.2974813533672035</v>
+        <v>0.2715276868700092</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06597280318096302</v>
+        <v>0.05638117108752808</v>
       </c>
       <c r="AC3">
-        <v>-0.06597280318096302</v>
+        <v>-0.05638117108752808</v>
       </c>
       <c r="AD3">
-        <v>3600.7</v>
+        <v>3910.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3600.7</v>
+        <v>3910.2</v>
       </c>
       <c r="AG3">
-        <v>1918</v>
+        <v>1068.5</v>
       </c>
       <c r="AH3">
-        <v>0.6570740341977044</v>
+        <v>0.7218386560827026</v>
       </c>
       <c r="AI3">
-        <v>0.640990493822765</v>
+        <v>0.6488989196634528</v>
       </c>
       <c r="AJ3">
-        <v>0.5051090277046244</v>
+        <v>0.4149031180833301</v>
       </c>
       <c r="AK3">
-        <v>0.4874577477317203</v>
+        <v>0.3355630927705546</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Georgia Group PLC (LSE:BGEO)</t>
+          <t>HSBC Holdings plc (LSE:HSBA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.236</v>
+        <v>0.0537</v>
       </c>
       <c r="E4">
-        <v>0.195</v>
+        <v>0.189</v>
       </c>
       <c r="F4">
-        <v>0.141</v>
+        <v>0.197</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.000506905719918081</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.0004587335330315984</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>353.7</v>
+        <v>28539</v>
       </c>
       <c r="L4">
-        <v>0.5598290598290598</v>
+        <v>0.4244601106550063</v>
       </c>
       <c r="M4">
-        <v>66.15000000000001</v>
+        <v>10062.527</v>
       </c>
       <c r="N4">
-        <v>0.04687832187655021</v>
+        <v>0.06547475495427028</v>
       </c>
       <c r="O4">
-        <v>0.1870229007633588</v>
+        <v>0.3525886330985669</v>
       </c>
       <c r="P4">
-        <v>66.15000000000001</v>
+        <v>10062.527</v>
       </c>
       <c r="Q4">
-        <v>0.04687832187655021</v>
+        <v>0.06547475495427028</v>
       </c>
       <c r="R4">
-        <v>0.1870229007633588</v>
+        <v>0.3525886330985669</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,67 +892,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>978.1</v>
+        <v>298779</v>
       </c>
       <c r="V4">
-        <v>0.6931471901353554</v>
+        <v>1.94409235478145</v>
       </c>
       <c r="W4">
-        <v>0.3815945625202287</v>
+        <v>0.1606392020668809</v>
       </c>
       <c r="X4">
-        <v>0.1031988650624544</v>
+        <v>0.1338373821918407</v>
       </c>
       <c r="Y4">
-        <v>0.2783956974577743</v>
+        <v>0.02680181987504024</v>
       </c>
       <c r="Z4">
-        <v>0.2719965377165626</v>
+        <v>0.1205747907659035</v>
       </c>
       <c r="AA4">
-        <v>0.0001247739327190812</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06975128295143913</v>
+        <v>0.0594151333056091</v>
       </c>
       <c r="AC4">
-        <v>-0.06962650901872006</v>
+        <v>-0.0594151333056091</v>
       </c>
       <c r="AD4">
-        <v>2050.6</v>
+        <v>698431</v>
       </c>
       <c r="AE4">
-        <v>1.423684830778782</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2052.023684830779</v>
+        <v>698431</v>
       </c>
       <c r="AG4">
-        <v>1073.923684830779</v>
+        <v>399652</v>
       </c>
       <c r="AH4">
-        <v>0.5925354886454333</v>
+        <v>0.8196425231007118</v>
       </c>
       <c r="AI4">
-        <v>0.6168673002955534</v>
+        <v>0.7862814388852051</v>
       </c>
       <c r="AJ4">
-        <v>0.4321583296715778</v>
+        <v>0.7222570813911796</v>
       </c>
       <c r="AK4">
-        <v>0.457295543290419</v>
+        <v>0.6779600062426632</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>3389.421487603306</v>
-      </c>
-      <c r="AP4">
-        <v>1775.080470794676</v>
       </c>
     </row>
     <row r="5">
@@ -975,10 +966,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.124</v>
+        <v>0.0466</v>
       </c>
       <c r="E5">
-        <v>0.146</v>
+        <v>0.00314</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -993,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>47</v>
+        <v>32.7</v>
       </c>
       <c r="L5">
-        <v>0.2547425474254743</v>
+        <v>0.1905594405594406</v>
       </c>
       <c r="M5">
-        <v>13.9</v>
+        <v>11.081</v>
       </c>
       <c r="N5">
-        <v>0.08229721728833629</v>
+        <v>0.06647270545890822</v>
       </c>
       <c r="O5">
-        <v>0.2957446808510638</v>
+        <v>0.338868501529052</v>
       </c>
       <c r="P5">
-        <v>13.9</v>
+        <v>10.7</v>
       </c>
       <c r="Q5">
-        <v>0.08229721728833629</v>
+        <v>0.06418716256748651</v>
       </c>
       <c r="R5">
-        <v>0.2957446808510638</v>
+        <v>0.3272171253822629</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.3810000000000002</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.03438317841350061</v>
       </c>
       <c r="U5">
-        <v>415.7</v>
+        <v>446.8</v>
       </c>
       <c r="V5">
-        <v>2.461219656601539</v>
+        <v>2.680263947210558</v>
       </c>
       <c r="W5">
-        <v>0.1178831201404565</v>
+        <v>0.0856020942408377</v>
       </c>
       <c r="X5">
-        <v>0.1453803668010036</v>
+        <v>0.122840802922248</v>
       </c>
       <c r="Y5">
-        <v>-0.02749724666054715</v>
+        <v>-0.03723870868141027</v>
       </c>
       <c r="Z5">
-        <v>0.2803951367781155</v>
+        <v>0.3298097251585624</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06979470656978146</v>
+        <v>0.05944414733221411</v>
       </c>
       <c r="AC5">
-        <v>-0.06979470656978146</v>
+        <v>-0.05944414733221411</v>
       </c>
       <c r="AD5">
-        <v>554</v>
+        <v>644.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>554</v>
+        <v>644.2</v>
       </c>
       <c r="AG5">
-        <v>138.3</v>
+        <v>197.4</v>
       </c>
       <c r="AH5">
-        <v>0.7663577258265321</v>
+        <v>0.7944259464792206</v>
       </c>
       <c r="AI5">
-        <v>0.5918803418803419</v>
+        <v>0.6034095166729113</v>
       </c>
       <c r="AJ5">
-        <v>0.4501953124999999</v>
+        <v>0.5421587475968142</v>
       </c>
       <c r="AK5">
-        <v>0.2658081875840861</v>
+        <v>0.3179768041237114</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc (LSE:HSBA)</t>
+          <t>Bank of Georgia Group PLC (LSE:BGEO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,13 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00138</v>
+        <v>0.226</v>
       </c>
       <c r="E6">
-        <v>0.152</v>
-      </c>
-      <c r="F6">
-        <v>0.183</v>
+        <v>0.286</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,97 +1100,103 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.0004892220673424463</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.0004240286016569727</v>
       </c>
       <c r="K6">
-        <v>13221</v>
+        <v>623.6</v>
       </c>
       <c r="L6">
-        <v>0.2860078743564228</v>
+        <v>0.7410576351752822</v>
       </c>
       <c r="M6">
-        <v>5328.504000000001</v>
+        <v>209.8</v>
       </c>
       <c r="N6">
-        <v>0.04345283635862488</v>
+        <v>0.0950138127802183</v>
       </c>
       <c r="O6">
-        <v>0.4030333560245065</v>
+        <v>0.336433611289288</v>
       </c>
       <c r="P6">
-        <v>5328.504000000001</v>
+        <v>77.7</v>
       </c>
       <c r="Q6">
-        <v>0.04345283635862488</v>
+        <v>0.03518862370363662</v>
       </c>
       <c r="R6">
-        <v>0.4030333560245065</v>
+        <v>0.1245991019884541</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>132.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.6296472831267875</v>
       </c>
       <c r="U6">
-        <v>309505</v>
+        <v>823.3</v>
       </c>
       <c r="V6">
-        <v>2.52394858241191</v>
+        <v>0.3728544902857661</v>
       </c>
       <c r="W6">
-        <v>0.07523473510499061</v>
+        <v>0.534407404233439</v>
       </c>
       <c r="X6">
-        <v>0.199497312647869</v>
+        <v>0.06890118887056529</v>
       </c>
       <c r="Y6">
-        <v>-0.1242625775428784</v>
+        <v>0.4655062153628737</v>
       </c>
       <c r="Z6">
-        <v>0.1328161588300363</v>
+        <v>0.3815830562364531</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.0001618021297519372</v>
       </c>
       <c r="AB6">
-        <v>0.0698153519975879</v>
+        <v>0.05996044064652029</v>
       </c>
       <c r="AC6">
-        <v>-0.0698153519975879</v>
+        <v>-0.05979863851676835</v>
       </c>
       <c r="AD6">
-        <v>689475</v>
+        <v>1165.1</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.586598151656657</v>
       </c>
       <c r="AF6">
-        <v>689475</v>
+        <v>1166.686598151657</v>
       </c>
       <c r="AG6">
-        <v>379970</v>
+        <v>343.3865981516567</v>
       </c>
       <c r="AH6">
-        <v>0.8490001813810895</v>
+        <v>0.3457067770716648</v>
       </c>
       <c r="AI6">
-        <v>0.7875502017206797</v>
+        <v>0.402529669056457</v>
       </c>
       <c r="AJ6">
-        <v>0.7560128158269056</v>
+        <v>0.1345829519153313</v>
       </c>
       <c r="AK6">
-        <v>0.6713689764171863</v>
+        <v>0.1654806110055945</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>1598.216735253772</v>
+      </c>
+      <c r="AP6">
+        <v>471.0378575468542</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
+          <t>Barclays PLC (LSE:BARC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,13 +1216,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.017</v>
+        <v>0.0364</v>
       </c>
       <c r="E7">
-        <v>0.06559999999999999</v>
+        <v>0.447</v>
       </c>
       <c r="F7">
-        <v>0.0374</v>
+        <v>0.0191</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1243,28 +1237,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>4856.1</v>
+        <v>7897.9</v>
       </c>
       <c r="L7">
-        <v>0.2689957734854066</v>
+        <v>0.2724597583777779</v>
       </c>
       <c r="M7">
-        <v>1536.8117</v>
+        <v>1421.9944</v>
       </c>
       <c r="N7">
-        <v>0.04203671072354671</v>
+        <v>0.04798911972353839</v>
       </c>
       <c r="O7">
-        <v>0.3164703568707398</v>
+        <v>0.1800471517745224</v>
       </c>
       <c r="P7">
-        <v>1536.8117</v>
+        <v>1421.9944</v>
       </c>
       <c r="Q7">
-        <v>0.04203671072354671</v>
+        <v>0.04798911972353839</v>
       </c>
       <c r="R7">
-        <v>0.3164703568707398</v>
+        <v>0.1800471517745224</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1273,55 +1267,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>94537.7</v>
+        <v>320699</v>
       </c>
       <c r="V7">
-        <v>2.58590818079368</v>
+        <v>10.82287152904332</v>
       </c>
       <c r="W7">
-        <v>0.06863871703649679</v>
+        <v>0.1057346158737809</v>
       </c>
       <c r="X7">
-        <v>0.184415680851683</v>
+        <v>0.5599956438676503</v>
       </c>
       <c r="Y7">
-        <v>-0.1157769638151862</v>
+        <v>-0.4542610279938695</v>
       </c>
       <c r="Z7">
-        <v>0.2285594551856246</v>
+        <v>0.04032015881363809</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07099752179897709</v>
+        <v>0.06021282006873493</v>
       </c>
       <c r="AC7">
-        <v>-0.07099752179897709</v>
+        <v>-0.06021282006873493</v>
       </c>
       <c r="AD7">
-        <v>181686.6</v>
+        <v>915664</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>181686.6</v>
+        <v>915664</v>
       </c>
       <c r="AG7">
-        <v>87148.90000000001</v>
+        <v>594965</v>
       </c>
       <c r="AH7">
-        <v>0.8324876492242218</v>
+        <v>0.9686536148057814</v>
       </c>
       <c r="AI7">
-        <v>0.778568878859546</v>
+        <v>0.9158148347032756</v>
       </c>
       <c r="AJ7">
-        <v>0.704474337490714</v>
+        <v>0.9525588195644997</v>
       </c>
       <c r="AK7">
-        <v>0.6277744161588221</v>
+        <v>0.8760612560394724</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1338,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Standard Chartered PLC (LSE:STAN)</t>
+          <t>NatWest Group plc (LSE:NWG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1347,13 +1341,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0307</v>
+        <v>0.0253</v>
       </c>
       <c r="E8">
-        <v>0.158</v>
+        <v>0.281</v>
       </c>
       <c r="F8">
-        <v>0.334</v>
+        <v>0.109</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1368,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>2814</v>
+        <v>5698.9</v>
       </c>
       <c r="L8">
-        <v>0.1892909995963944</v>
+        <v>0.322337796028258</v>
       </c>
       <c r="M8">
-        <v>376.74</v>
+        <v>1661.6124</v>
       </c>
       <c r="N8">
-        <v>0.01733484868702578</v>
+        <v>0.06763016960328218</v>
       </c>
       <c r="O8">
-        <v>0.1338805970149254</v>
+        <v>0.2915672147256488</v>
       </c>
       <c r="P8">
-        <v>376.74</v>
+        <v>1661.6124</v>
       </c>
       <c r="Q8">
-        <v>0.01733484868702578</v>
+        <v>0.06763016960328218</v>
       </c>
       <c r="R8">
-        <v>0.1338805970149254</v>
+        <v>0.2915672147256488</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1398,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>66521</v>
+        <v>156254.1</v>
       </c>
       <c r="V8">
-        <v>3.060815070100446</v>
+        <v>6.359781188566126</v>
       </c>
       <c r="W8">
-        <v>0.0547194026367985</v>
+        <v>0.1463586890921185</v>
       </c>
       <c r="X8">
-        <v>0.2617662726074869</v>
+        <v>0.1843042196769272</v>
       </c>
       <c r="Y8">
-        <v>-0.2070468699706884</v>
+        <v>-0.03794553058480871</v>
       </c>
       <c r="Z8">
-        <v>0.07928660191896404</v>
+        <v>0.2709019338646187</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07109833172370217</v>
+        <v>0.06022543534424361</v>
       </c>
       <c r="AC8">
-        <v>-0.07109833172370217</v>
+        <v>-0.06022543534424361</v>
       </c>
       <c r="AD8">
-        <v>180773</v>
+        <v>188342.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>180773</v>
+        <v>188342.3</v>
       </c>
       <c r="AG8">
-        <v>114252</v>
+        <v>32088.19999999998</v>
       </c>
       <c r="AH8">
-        <v>0.8926792822537197</v>
+        <v>0.8846041123208996</v>
       </c>
       <c r="AI8">
-        <v>0.7833266890837869</v>
+        <v>0.8131837434318749</v>
       </c>
       <c r="AJ8">
-        <v>0.8401802844576354</v>
+        <v>0.5663559682512226</v>
       </c>
       <c r="AK8">
-        <v>0.6955769991781072</v>
+        <v>0.4258163486024504</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1463,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NatWest Group plc (LSE:NWG)</t>
+          <t>Standard Chartered PLC (LSE:STAN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1472,10 +1466,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0104</v>
+        <v>0.0177</v>
+      </c>
+      <c r="E9">
+        <v>0.0506</v>
       </c>
       <c r="F9">
-        <v>0.31</v>
+        <v>0.251</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1490,28 +1487,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3078.8</v>
+        <v>2305</v>
       </c>
       <c r="L9">
-        <v>0.2217676294748974</v>
+        <v>0.1476806765761148</v>
       </c>
       <c r="M9">
-        <v>1245.7788</v>
+        <v>526.98</v>
       </c>
       <c r="N9">
-        <v>0.04037107802788238</v>
+        <v>0.02355502116456511</v>
       </c>
       <c r="O9">
-        <v>0.4046312849162011</v>
+        <v>0.2286247288503254</v>
       </c>
       <c r="P9">
-        <v>1245.7788</v>
+        <v>526.98</v>
       </c>
       <c r="Q9">
-        <v>0.04037107802788238</v>
+        <v>0.02355502116456511</v>
       </c>
       <c r="R9">
-        <v>0.4046312849162011</v>
+        <v>0.2286247288503254</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1520,55 +1517,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>183657.8</v>
+        <v>89137</v>
       </c>
       <c r="V9">
-        <v>5.951669248368343</v>
+        <v>3.984257318201526</v>
       </c>
       <c r="W9">
-        <v>0.05510403150029084</v>
+        <v>0.04788217453623881</v>
       </c>
       <c r="X9">
-        <v>0.2268101069479499</v>
+        <v>0.174864901880538</v>
       </c>
       <c r="Y9">
-        <v>-0.1717060754476591</v>
+        <v>-0.1269827273442992</v>
       </c>
       <c r="Z9">
-        <v>0.4496824075483673</v>
+        <v>0.09523751411050432</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07230590482702791</v>
+        <v>0.06022668646394111</v>
       </c>
       <c r="AC9">
-        <v>-0.07230590482702791</v>
+        <v>-0.06022668646394111</v>
       </c>
       <c r="AD9">
-        <v>209983</v>
+        <v>158441</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>209983</v>
+        <v>158441</v>
       </c>
       <c r="AG9">
-        <v>26325.20000000001</v>
+        <v>69304</v>
       </c>
       <c r="AH9">
-        <v>0.8718732509221844</v>
+        <v>0.8762685045845633</v>
       </c>
       <c r="AI9">
-        <v>0.8435281291200646</v>
+        <v>0.7661668206018463</v>
       </c>
       <c r="AJ9">
-        <v>0.4603643714784362</v>
+        <v>0.755964191399522</v>
       </c>
       <c r="AK9">
-        <v>0.4032881715290673</v>
+        <v>0.5890192078871325</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1585,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barclays PLC (LSE:BARC)</t>
+          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1594,13 +1591,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.04389999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="E10">
-        <v>1.442</v>
+        <v>0.09</v>
       </c>
       <c r="F10">
-        <v>0.00148</v>
+        <v>0.0625</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1615,28 +1612,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>6578.8</v>
+        <v>8331.1</v>
       </c>
       <c r="L10">
-        <v>0.2499154766924605</v>
+        <v>0.3432037735071783</v>
       </c>
       <c r="M10">
-        <v>1110.396</v>
+        <v>1959.9843</v>
       </c>
       <c r="N10">
-        <v>0.03664939368535009</v>
+        <v>0.05101123557489603</v>
       </c>
       <c r="O10">
-        <v>0.1687839727609898</v>
+        <v>0.235261165992486</v>
       </c>
       <c r="P10">
-        <v>1110.396</v>
+        <v>1959.9843</v>
       </c>
       <c r="Q10">
-        <v>0.03664939368535009</v>
+        <v>0.05101123557489603</v>
       </c>
       <c r="R10">
-        <v>0.1687839727609898</v>
+        <v>0.235261165992486</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1645,55 +1642,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>286451.3</v>
+        <v>106778.9</v>
       </c>
       <c r="V10">
-        <v>9.454524750972018</v>
+        <v>2.779064925330404</v>
       </c>
       <c r="W10">
-        <v>0.07092869934222655</v>
+        <v>0.1620061215838334</v>
       </c>
       <c r="X10">
-        <v>0.7792631096858946</v>
+        <v>0.1435729716997858</v>
       </c>
       <c r="Y10">
-        <v>-0.7083344103436681</v>
+        <v>0.01843314988404765</v>
       </c>
       <c r="Z10">
-        <v>0.04002575116040634</v>
+        <v>0.1751741855405254</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07260534356306238</v>
+        <v>0.06023253382984779</v>
       </c>
       <c r="AC10">
-        <v>-0.07260534356306238</v>
+        <v>-0.06023253382984779</v>
       </c>
       <c r="AD10">
-        <v>930686.5</v>
+        <v>197748.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>930686.5</v>
+        <v>197748.5</v>
       </c>
       <c r="AG10">
-        <v>644235.2</v>
+        <v>90969.60000000001</v>
       </c>
       <c r="AH10">
-        <v>0.9684721175985913</v>
+        <v>0.8373103228972554</v>
       </c>
       <c r="AI10">
-        <v>0.9247112011603421</v>
+        <v>0.7826202760939057</v>
       </c>
       <c r="AJ10">
-        <v>0.955083294664605</v>
+        <v>0.703053197951654</v>
       </c>
       <c r="AK10">
-        <v>0.8947580625560321</v>
+        <v>0.6235236058562263</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1719,13 +1716,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.11</v>
-      </c>
-      <c r="E11">
-        <v>0.262</v>
+        <v>0.0946</v>
       </c>
       <c r="F11">
-        <v>-0.0387</v>
+        <v>0.0746</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1740,85 +1734,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>520.4</v>
+        <v>234.3</v>
       </c>
       <c r="L11">
-        <v>0.2806601229640815</v>
+        <v>0.1264845605700713</v>
       </c>
       <c r="M11">
-        <v>876.9000000000001</v>
+        <v>471</v>
       </c>
       <c r="N11">
-        <v>0.2907782604370462</v>
+        <v>0.1711731356301788</v>
       </c>
       <c r="O11">
-        <v>1.685049961568025</v>
+        <v>2.010243277848911</v>
       </c>
       <c r="P11">
-        <v>133.7</v>
+        <v>246.5</v>
       </c>
       <c r="Q11">
-        <v>0.04433464867195012</v>
+        <v>0.08958424189562436</v>
       </c>
       <c r="R11">
-        <v>0.2569177555726364</v>
+        <v>1.052069995731967</v>
       </c>
       <c r="S11">
-        <v>743.2</v>
+        <v>224.5</v>
       </c>
       <c r="T11">
-        <v>0.8475310753791766</v>
+        <v>0.4766454352441614</v>
       </c>
       <c r="U11">
-        <v>1806.3</v>
+        <v>1817.1</v>
       </c>
       <c r="V11">
-        <v>0.5989654143316643</v>
+        <v>0.6603794156127344</v>
       </c>
       <c r="W11">
-        <v>0.07042425062588809</v>
+        <v>0.03316535968066132</v>
       </c>
       <c r="X11">
-        <v>0.2183055593235964</v>
+        <v>0.182625593256981</v>
       </c>
       <c r="Y11">
-        <v>-0.1478813086977083</v>
+        <v>-0.1494602335763197</v>
       </c>
       <c r="Z11">
-        <v>0.07964468727583557</v>
+        <v>0.07512673885711968</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07364945548960727</v>
+        <v>0.06200287434723878</v>
       </c>
       <c r="AC11">
-        <v>-0.07364945548960727</v>
+        <v>-0.06200287434723878</v>
       </c>
       <c r="AD11">
-        <v>19411</v>
+        <v>20807.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>19411</v>
+        <v>20807.6</v>
       </c>
       <c r="AG11">
-        <v>17604.7</v>
+        <v>18990.5</v>
       </c>
       <c r="AH11">
-        <v>0.8655308181765484</v>
+        <v>0.8832048626438929</v>
       </c>
       <c r="AI11">
-        <v>0.7331656317514995</v>
+        <v>0.7525379838625095</v>
       </c>
       <c r="AJ11">
-        <v>0.8537516246047603</v>
+        <v>0.873443687592275</v>
       </c>
       <c r="AK11">
-        <v>0.7136278694571795</v>
+        <v>0.7351313059366387</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0364</v>
+        <v>0.0283</v>
       </c>
       <c r="E2">
-        <v>0.1395</v>
+        <v>0.138</v>
       </c>
       <c r="F2">
-        <v>0.09179999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2.610720697709334e-06</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1.962337555980011e-06</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>53766.8</v>
+        <v>48090.8</v>
       </c>
       <c r="L2">
-        <v>0.3409686444912879</v>
+        <v>0.317026317558971</v>
       </c>
       <c r="M2">
-        <v>16458.9091</v>
+        <v>17973.3635</v>
       </c>
       <c r="N2">
-        <v>0.05978223115100409</v>
+        <v>0.05386462071358915</v>
       </c>
       <c r="O2">
-        <v>0.3061165830958882</v>
+        <v>0.3737380850391342</v>
       </c>
       <c r="P2">
-        <v>16095.4981</v>
+        <v>17973.3635</v>
       </c>
       <c r="Q2">
-        <v>0.0584622457089059</v>
+        <v>0.05386462071358915</v>
       </c>
       <c r="R2">
-        <v>0.2993575607996013</v>
+        <v>0.3737380850391342</v>
       </c>
       <c r="S2">
-        <v>363.4110000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.02207989592700284</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>977576.9</v>
+        <v>835224.7000000001</v>
       </c>
       <c r="V2">
-        <v>3.550765597440598</v>
+        <v>2.503096411315628</v>
       </c>
       <c r="W2">
-        <v>0.1057346158737809</v>
+        <v>0.1215780335505023</v>
       </c>
       <c r="X2">
-        <v>0.1435729716997858</v>
+        <v>0.1344123212962882</v>
       </c>
       <c r="Y2">
-        <v>-0.03783835582600489</v>
+        <v>-0.01283428774578595</v>
       </c>
       <c r="Z2">
-        <v>0.09411516775476092</v>
+        <v>0.09487216467172115</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06021282006873493</v>
+        <v>0.06259031723364959</v>
       </c>
       <c r="AC2">
-        <v>-0.06021282006873493</v>
+        <v>-0.06259031723364959</v>
       </c>
       <c r="AD2">
-        <v>2185153.9</v>
+        <v>2174899.8</v>
       </c>
       <c r="AE2">
-        <v>1.586598151656657</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>2185155.486598152</v>
+        <v>2174899.8</v>
       </c>
       <c r="AG2">
-        <v>1207578.586598152</v>
+        <v>1339675.1</v>
       </c>
       <c r="AH2">
-        <v>0.888104950400084</v>
+        <v>0.8669856736274805</v>
       </c>
       <c r="AI2">
-        <v>0.8350388304744233</v>
+        <v>0.8245935845938348</v>
       </c>
       <c r="AJ2">
-        <v>0.8143396708405857</v>
+        <v>0.8005938620076102</v>
       </c>
       <c r="AK2">
-        <v>0.7366634596008048</v>
+        <v>0.7433072254555914</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>2997467.626886145</v>
-      </c>
-      <c r="AP2">
-        <v>1656486.401369207</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Close Brothers Group plc (LSE:CBG)</t>
+          <t>HSBC Holdings plc (LSE:HSBA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00052</v>
+        <v>0.0195</v>
       </c>
       <c r="E3">
-        <v>-0.167</v>
+        <v>0.103</v>
+      </c>
+      <c r="F3">
+        <v>0.169</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>104.3</v>
+        <v>23600</v>
       </c>
       <c r="L3">
-        <v>0.1005688940314338</v>
+        <v>0.4071071243746766</v>
       </c>
       <c r="M3">
-        <v>133.93</v>
+        <v>10780.652</v>
       </c>
       <c r="N3">
-        <v>0.08888372710379613</v>
+        <v>0.0620464180432503</v>
       </c>
       <c r="O3">
-        <v>1.284084372003835</v>
+        <v>0.4568072881355932</v>
       </c>
       <c r="P3">
-        <v>127.5</v>
+        <v>10780.652</v>
       </c>
       <c r="Q3">
-        <v>0.08461640562782055</v>
+        <v>0.0620464180432503</v>
       </c>
       <c r="R3">
-        <v>1.222435282837967</v>
+        <v>0.4568072881355932</v>
       </c>
       <c r="S3">
-        <v>6.430000000000007</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.04801015455835143</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2841.7</v>
+        <v>252310</v>
       </c>
       <c r="V3">
-        <v>1.885917175471197</v>
+        <v>1.452132184258659</v>
       </c>
       <c r="W3">
-        <v>0.05171815341895175</v>
+        <v>0.1291593695271454</v>
       </c>
       <c r="X3">
-        <v>0.1023164514801041</v>
+        <v>0.1287580685930172</v>
       </c>
       <c r="Y3">
-        <v>-0.05059829806115237</v>
+        <v>0.0004013009341281848</v>
       </c>
       <c r="Z3">
-        <v>0.2715276868700092</v>
+        <v>0.09954118673287864</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05638117108752808</v>
+        <v>0.06203848417014039</v>
       </c>
       <c r="AC3">
-        <v>-0.05638117108752808</v>
+        <v>-0.06203848417014039</v>
       </c>
       <c r="AD3">
-        <v>3910.2</v>
+        <v>719546</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3910.2</v>
+        <v>719546</v>
       </c>
       <c r="AG3">
-        <v>1068.5</v>
+        <v>467236</v>
       </c>
       <c r="AH3">
-        <v>0.7218386560827026</v>
+        <v>0.8054943404066776</v>
       </c>
       <c r="AI3">
-        <v>0.6488989196634528</v>
+        <v>0.7824800912599462</v>
       </c>
       <c r="AJ3">
-        <v>0.4149031180833301</v>
+        <v>0.7289316451462228</v>
       </c>
       <c r="AK3">
-        <v>0.3355630927705546</v>
+        <v>0.7002297451821701</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc (LSE:HSBA)</t>
+          <t>Barclays PLC (LSE:BARC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0537</v>
+        <v>0.0392</v>
       </c>
       <c r="E4">
-        <v>0.189</v>
+        <v>0.148</v>
       </c>
       <c r="F4">
-        <v>0.197</v>
+        <v>0.164</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>28539</v>
+        <v>6999.1</v>
       </c>
       <c r="L4">
-        <v>0.4244601106550063</v>
+        <v>0.2212818291611076</v>
       </c>
       <c r="M4">
-        <v>10062.527</v>
+        <v>1582.416</v>
       </c>
       <c r="N4">
-        <v>0.06547475495427028</v>
+        <v>0.03276691701298944</v>
       </c>
       <c r="O4">
-        <v>0.3525886330985669</v>
+        <v>0.2260884970924833</v>
       </c>
       <c r="P4">
-        <v>10062.527</v>
+        <v>1582.416</v>
       </c>
       <c r="Q4">
-        <v>0.06547475495427028</v>
+        <v>0.03276691701298944</v>
       </c>
       <c r="R4">
-        <v>0.3525886330985669</v>
+        <v>0.2260884970924833</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>298779</v>
+        <v>288246.9</v>
       </c>
       <c r="V4">
-        <v>1.94409235478145</v>
+        <v>5.968697391552832</v>
       </c>
       <c r="W4">
-        <v>0.1606392020668809</v>
+        <v>0.08395638984284942</v>
       </c>
       <c r="X4">
-        <v>0.1338373821918407</v>
+        <v>0.3608937229360646</v>
       </c>
       <c r="Y4">
-        <v>0.02680181987504024</v>
+        <v>-0.2769373330932152</v>
       </c>
       <c r="Z4">
-        <v>0.1205747907659035</v>
+        <v>0.04662886505686236</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0594151333056091</v>
+        <v>0.06210612775214323</v>
       </c>
       <c r="AC4">
-        <v>-0.0594151333056091</v>
+        <v>-0.06210612775214323</v>
       </c>
       <c r="AD4">
-        <v>698431</v>
+        <v>939800.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>698431</v>
+        <v>939800.3</v>
       </c>
       <c r="AG4">
-        <v>399652</v>
+        <v>651553.4</v>
       </c>
       <c r="AH4">
-        <v>0.8196425231007118</v>
+        <v>0.9511249645023436</v>
       </c>
       <c r="AI4">
-        <v>0.7862814388852051</v>
+        <v>0.9073105087241479</v>
       </c>
       <c r="AJ4">
-        <v>0.7222570813911796</v>
+        <v>0.930994725271899</v>
       </c>
       <c r="AK4">
-        <v>0.6779600062426632</v>
+        <v>0.8715710536383605</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secure Trust Bank PLC (LSE:STB)</t>
+          <t>Standard Chartered PLC (LSE:STAN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,10 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0466</v>
+        <v>0.0529</v>
       </c>
       <c r="E5">
-        <v>0.00314</v>
+        <v>0.364</v>
+      </c>
+      <c r="F5">
+        <v>0.11</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>32.7</v>
+        <v>4464</v>
       </c>
       <c r="L5">
-        <v>0.1905594405594406</v>
+        <v>0.2417677642980936</v>
       </c>
       <c r="M5">
-        <v>11.081</v>
+        <v>719.64</v>
       </c>
       <c r="N5">
-        <v>0.06647270545890822</v>
+        <v>0.02423928054161474</v>
       </c>
       <c r="O5">
-        <v>0.338868501529052</v>
+        <v>0.1612096774193548</v>
       </c>
       <c r="P5">
-        <v>10.7</v>
+        <v>719.64</v>
       </c>
       <c r="Q5">
-        <v>0.06418716256748651</v>
+        <v>0.02423928054161474</v>
       </c>
       <c r="R5">
-        <v>0.3272171253822629</v>
+        <v>0.1612096774193548</v>
       </c>
       <c r="S5">
-        <v>0.3810000000000002</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.03438317841350061</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>446.8</v>
+        <v>64905</v>
       </c>
       <c r="V5">
-        <v>2.680263947210558</v>
+        <v>2.18616322543703</v>
       </c>
       <c r="W5">
-        <v>0.0856020942408377</v>
+        <v>0.09603304362791498</v>
       </c>
       <c r="X5">
-        <v>0.122840802922248</v>
+        <v>0.1415848784993639</v>
       </c>
       <c r="Y5">
-        <v>-0.03723870868141027</v>
+        <v>-0.04555183487144895</v>
       </c>
       <c r="Z5">
-        <v>0.3298097251585624</v>
+        <v>0.1574325130881124</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05944414733221411</v>
+        <v>0.06259031723364959</v>
       </c>
       <c r="AC5">
-        <v>-0.05944414733221411</v>
+        <v>-0.06259031723364959</v>
       </c>
       <c r="AD5">
-        <v>644.2</v>
+        <v>148080</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>644.2</v>
+        <v>148080</v>
       </c>
       <c r="AG5">
-        <v>197.4</v>
+        <v>83175</v>
       </c>
       <c r="AH5">
-        <v>0.7944259464792206</v>
+        <v>0.8329911289369912</v>
       </c>
       <c r="AI5">
-        <v>0.6034095166729113</v>
+        <v>0.7373914429129153</v>
       </c>
       <c r="AJ5">
-        <v>0.5421587475968142</v>
+        <v>0.7369488942444004</v>
       </c>
       <c r="AK5">
-        <v>0.3179768041237114</v>
+        <v>0.6119813701613556</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank of Georgia Group PLC (LSE:BGEO)</t>
+          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.226</v>
+        <v>0.0186</v>
       </c>
       <c r="E6">
-        <v>0.286</v>
+        <v>0.133</v>
+      </c>
+      <c r="F6">
+        <v>0.03759999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,103 +1103,97 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0004892220673424463</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.0004240286016569727</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>623.6</v>
+        <v>6645.2</v>
       </c>
       <c r="L6">
-        <v>0.7410576351752822</v>
+        <v>0.2671469404656137</v>
       </c>
       <c r="M6">
-        <v>209.8</v>
+        <v>2360.67</v>
       </c>
       <c r="N6">
-        <v>0.0950138127802183</v>
+        <v>0.05686744491927596</v>
       </c>
       <c r="O6">
-        <v>0.336433611289288</v>
+        <v>0.3552443869259014</v>
       </c>
       <c r="P6">
-        <v>77.7</v>
+        <v>2360.67</v>
       </c>
       <c r="Q6">
-        <v>0.03518862370363662</v>
+        <v>0.05686744491927596</v>
       </c>
       <c r="R6">
-        <v>0.1245991019884541</v>
+        <v>0.3552443869259014</v>
       </c>
       <c r="S6">
-        <v>132.1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.6296472831267875</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>823.3</v>
+        <v>79151.60000000001</v>
       </c>
       <c r="V6">
-        <v>0.3728544902857661</v>
+        <v>1.906725316656951</v>
       </c>
       <c r="W6">
-        <v>0.534407404233439</v>
+        <v>0.1215780335505023</v>
       </c>
       <c r="X6">
-        <v>0.06890118887056529</v>
+        <v>0.1344123212962882</v>
       </c>
       <c r="Y6">
-        <v>0.4655062153628737</v>
+        <v>-0.01283428774578595</v>
       </c>
       <c r="Z6">
-        <v>0.3815830562364531</v>
+        <v>0.170810458189559</v>
       </c>
       <c r="AA6">
-        <v>0.0001618021297519372</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05996044064652029</v>
+        <v>0.06264907291991287</v>
       </c>
       <c r="AC6">
-        <v>-0.05979863851676835</v>
+        <v>-0.06264907291991287</v>
       </c>
       <c r="AD6">
-        <v>1165.1</v>
+        <v>187399.8</v>
       </c>
       <c r="AE6">
-        <v>1.586598151656657</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1166.686598151657</v>
+        <v>187399.8</v>
       </c>
       <c r="AG6">
-        <v>343.3865981516567</v>
+        <v>108248.2</v>
       </c>
       <c r="AH6">
-        <v>0.3457067770716648</v>
+        <v>0.8186557605643402</v>
       </c>
       <c r="AI6">
-        <v>0.402529669056457</v>
+        <v>0.7507463404081436</v>
       </c>
       <c r="AJ6">
-        <v>0.1345829519153313</v>
+        <v>0.7228111645299145</v>
       </c>
       <c r="AK6">
-        <v>0.1654806110055945</v>
+        <v>0.6350119437026887</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1598.216735253772</v>
-      </c>
-      <c r="AP6">
-        <v>471.0378575468542</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Barclays PLC (LSE:BARC)</t>
+          <t>NatWest Group plc (LSE:NWG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,13 +1213,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0364</v>
+        <v>0.0283</v>
       </c>
       <c r="E7">
-        <v>0.447</v>
+        <v>0.138</v>
       </c>
       <c r="F7">
-        <v>0.0191</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,28 +1234,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7897.9</v>
+        <v>6382.5</v>
       </c>
       <c r="L7">
-        <v>0.2724597583777779</v>
+        <v>0.3403110653749153</v>
       </c>
       <c r="M7">
-        <v>1421.9944</v>
+        <v>2529.9855</v>
       </c>
       <c r="N7">
-        <v>0.04798911972353839</v>
+        <v>0.06257492338856281</v>
       </c>
       <c r="O7">
-        <v>0.1800471517745224</v>
+        <v>0.3963941245593419</v>
       </c>
       <c r="P7">
-        <v>1421.9944</v>
+        <v>2529.9855</v>
       </c>
       <c r="Q7">
-        <v>0.04798911972353839</v>
+        <v>0.06257492338856281</v>
       </c>
       <c r="R7">
-        <v>0.1800471517745224</v>
+        <v>0.3963941245593419</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1267,557 +1264,60 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>320699</v>
+        <v>150611.2</v>
       </c>
       <c r="V7">
-        <v>10.82287152904332</v>
+        <v>3.725113958739887</v>
       </c>
       <c r="W7">
-        <v>0.1057346158737809</v>
+        <v>0.1476623881398125</v>
       </c>
       <c r="X7">
-        <v>0.5599956438676503</v>
+        <v>0.1334947101023821</v>
       </c>
       <c r="Y7">
-        <v>-0.4542610279938695</v>
+        <v>0.01416767803743041</v>
       </c>
       <c r="Z7">
-        <v>0.04032015881363809</v>
+        <v>0.2490300324783102</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06021282006873493</v>
+        <v>0.06265732558667859</v>
       </c>
       <c r="AC7">
-        <v>-0.06021282006873493</v>
+        <v>-0.06265732558667859</v>
       </c>
       <c r="AD7">
-        <v>915664</v>
+        <v>180073.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>915664</v>
+        <v>180073.7</v>
       </c>
       <c r="AG7">
-        <v>594965</v>
+        <v>29462.5</v>
       </c>
       <c r="AH7">
-        <v>0.9686536148057814</v>
+        <v>0.8166422530101359</v>
       </c>
       <c r="AI7">
-        <v>0.9158148347032756</v>
+        <v>0.7770921547541165</v>
       </c>
       <c r="AJ7">
-        <v>0.9525588195644997</v>
+        <v>0.4215323819852405</v>
       </c>
       <c r="AK7">
-        <v>0.8760612560394724</v>
+        <v>0.3632126179169687</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NatWest Group plc (LSE:NWG)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0253</v>
-      </c>
-      <c r="E8">
-        <v>0.281</v>
-      </c>
-      <c r="F8">
-        <v>0.109</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>5698.9</v>
-      </c>
-      <c r="L8">
-        <v>0.322337796028258</v>
-      </c>
-      <c r="M8">
-        <v>1661.6124</v>
-      </c>
-      <c r="N8">
-        <v>0.06763016960328218</v>
-      </c>
-      <c r="O8">
-        <v>0.2915672147256488</v>
-      </c>
-      <c r="P8">
-        <v>1661.6124</v>
-      </c>
-      <c r="Q8">
-        <v>0.06763016960328218</v>
-      </c>
-      <c r="R8">
-        <v>0.2915672147256488</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>156254.1</v>
-      </c>
-      <c r="V8">
-        <v>6.359781188566126</v>
-      </c>
-      <c r="W8">
-        <v>0.1463586890921185</v>
-      </c>
-      <c r="X8">
-        <v>0.1843042196769272</v>
-      </c>
-      <c r="Y8">
-        <v>-0.03794553058480871</v>
-      </c>
-      <c r="Z8">
-        <v>0.2709019338646187</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.06022543534424361</v>
-      </c>
-      <c r="AC8">
-        <v>-0.06022543534424361</v>
-      </c>
-      <c r="AD8">
-        <v>188342.3</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>188342.3</v>
-      </c>
-      <c r="AG8">
-        <v>32088.19999999998</v>
-      </c>
-      <c r="AH8">
-        <v>0.8846041123208996</v>
-      </c>
-      <c r="AI8">
-        <v>0.8131837434318749</v>
-      </c>
-      <c r="AJ8">
-        <v>0.5663559682512226</v>
-      </c>
-      <c r="AK8">
-        <v>0.4258163486024504</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Standard Chartered PLC (LSE:STAN)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.0177</v>
-      </c>
-      <c r="E9">
-        <v>0.0506</v>
-      </c>
-      <c r="F9">
-        <v>0.251</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>2305</v>
-      </c>
-      <c r="L9">
-        <v>0.1476806765761148</v>
-      </c>
-      <c r="M9">
-        <v>526.98</v>
-      </c>
-      <c r="N9">
-        <v>0.02355502116456511</v>
-      </c>
-      <c r="O9">
-        <v>0.2286247288503254</v>
-      </c>
-      <c r="P9">
-        <v>526.98</v>
-      </c>
-      <c r="Q9">
-        <v>0.02355502116456511</v>
-      </c>
-      <c r="R9">
-        <v>0.2286247288503254</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>89137</v>
-      </c>
-      <c r="V9">
-        <v>3.984257318201526</v>
-      </c>
-      <c r="W9">
-        <v>0.04788217453623881</v>
-      </c>
-      <c r="X9">
-        <v>0.174864901880538</v>
-      </c>
-      <c r="Y9">
-        <v>-0.1269827273442992</v>
-      </c>
-      <c r="Z9">
-        <v>0.09523751411050432</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.06022668646394111</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06022668646394111</v>
-      </c>
-      <c r="AD9">
-        <v>158441</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>158441</v>
-      </c>
-      <c r="AG9">
-        <v>69304</v>
-      </c>
-      <c r="AH9">
-        <v>0.8762685045845633</v>
-      </c>
-      <c r="AI9">
-        <v>0.7661668206018463</v>
-      </c>
-      <c r="AJ9">
-        <v>0.755964191399522</v>
-      </c>
-      <c r="AK9">
-        <v>0.5890192078871325</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.0225</v>
-      </c>
-      <c r="E10">
-        <v>0.09</v>
-      </c>
-      <c r="F10">
-        <v>0.0625</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>8331.1</v>
-      </c>
-      <c r="L10">
-        <v>0.3432037735071783</v>
-      </c>
-      <c r="M10">
-        <v>1959.9843</v>
-      </c>
-      <c r="N10">
-        <v>0.05101123557489603</v>
-      </c>
-      <c r="O10">
-        <v>0.235261165992486</v>
-      </c>
-      <c r="P10">
-        <v>1959.9843</v>
-      </c>
-      <c r="Q10">
-        <v>0.05101123557489603</v>
-      </c>
-      <c r="R10">
-        <v>0.235261165992486</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>106778.9</v>
-      </c>
-      <c r="V10">
-        <v>2.779064925330404</v>
-      </c>
-      <c r="W10">
-        <v>0.1620061215838334</v>
-      </c>
-      <c r="X10">
-        <v>0.1435729716997858</v>
-      </c>
-      <c r="Y10">
-        <v>0.01843314988404765</v>
-      </c>
-      <c r="Z10">
-        <v>0.1751741855405254</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.06023253382984779</v>
-      </c>
-      <c r="AC10">
-        <v>-0.06023253382984779</v>
-      </c>
-      <c r="AD10">
-        <v>197748.5</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>197748.5</v>
-      </c>
-      <c r="AG10">
-        <v>90969.60000000001</v>
-      </c>
-      <c r="AH10">
-        <v>0.8373103228972554</v>
-      </c>
-      <c r="AI10">
-        <v>0.7826202760939057</v>
-      </c>
-      <c r="AJ10">
-        <v>0.703053197951654</v>
-      </c>
-      <c r="AK10">
-        <v>0.6235236058562263</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Virgin Money UK PLC (LSE:VMUK)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.0946</v>
-      </c>
-      <c r="F11">
-        <v>0.0746</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>234.3</v>
-      </c>
-      <c r="L11">
-        <v>0.1264845605700713</v>
-      </c>
-      <c r="M11">
-        <v>471</v>
-      </c>
-      <c r="N11">
-        <v>0.1711731356301788</v>
-      </c>
-      <c r="O11">
-        <v>2.010243277848911</v>
-      </c>
-      <c r="P11">
-        <v>246.5</v>
-      </c>
-      <c r="Q11">
-        <v>0.08958424189562436</v>
-      </c>
-      <c r="R11">
-        <v>1.052069995731967</v>
-      </c>
-      <c r="S11">
-        <v>224.5</v>
-      </c>
-      <c r="T11">
-        <v>0.4766454352441614</v>
-      </c>
-      <c r="U11">
-        <v>1817.1</v>
-      </c>
-      <c r="V11">
-        <v>0.6603794156127344</v>
-      </c>
-      <c r="W11">
-        <v>0.03316535968066132</v>
-      </c>
-      <c r="X11">
-        <v>0.182625593256981</v>
-      </c>
-      <c r="Y11">
-        <v>-0.1494602335763197</v>
-      </c>
-      <c r="Z11">
-        <v>0.07512673885711968</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.06200287434723878</v>
-      </c>
-      <c r="AC11">
-        <v>-0.06200287434723878</v>
-      </c>
-      <c r="AD11">
-        <v>20807.6</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>20807.6</v>
-      </c>
-      <c r="AG11">
-        <v>18990.5</v>
-      </c>
-      <c r="AH11">
-        <v>0.8832048626438929</v>
-      </c>
-      <c r="AI11">
-        <v>0.7525379838625095</v>
-      </c>
-      <c r="AJ11">
-        <v>0.873443687592275</v>
-      </c>
-      <c r="AK11">
-        <v>0.7351313059366387</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -594,7 +594,7 @@
         <v>0.138</v>
       </c>
       <c r="F2">
-        <v>0.11</v>
+        <v>0.137</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2.616402858283847E-06</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2.029815033890994E-06</v>
       </c>
       <c r="K2">
-        <v>48090.8</v>
+        <v>49551.3</v>
       </c>
       <c r="L2">
-        <v>0.317026317558971</v>
+        <v>0.3194506495541025</v>
       </c>
       <c r="M2">
-        <v>17973.3635</v>
+        <v>18399.6135</v>
       </c>
       <c r="N2">
-        <v>0.05386462071358915</v>
+        <v>0.05429179294445626</v>
       </c>
       <c r="O2">
-        <v>0.3737380850391342</v>
+        <v>0.3713245363895599</v>
       </c>
       <c r="P2">
-        <v>17973.3635</v>
+        <v>18393.1035</v>
       </c>
       <c r="Q2">
-        <v>0.05386462071358915</v>
+        <v>0.05427258386856625</v>
       </c>
       <c r="R2">
-        <v>0.3737380850391342</v>
+        <v>0.3711931573944579</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>6.509999999999995</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0003538117797963525</v>
       </c>
       <c r="U2">
-        <v>835224.7000000001</v>
+        <v>841263</v>
       </c>
       <c r="V2">
-        <v>2.503096411315628</v>
+        <v>2.482317175185887</v>
       </c>
       <c r="W2">
         <v>0.1215780335505023</v>
       </c>
       <c r="X2">
-        <v>0.1344123212962882</v>
+        <v>0.134370938468619</v>
       </c>
       <c r="Y2">
-        <v>-0.01283428774578595</v>
+        <v>-0.01279290491811667</v>
       </c>
       <c r="Z2">
-        <v>0.09487216467172115</v>
+        <v>0.09661971216027165</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06259031723364959</v>
+        <v>0.06258284651223123</v>
       </c>
       <c r="AC2">
-        <v>-0.06259031723364959</v>
+        <v>-0.06209893569902405</v>
       </c>
       <c r="AD2">
-        <v>2174899.8</v>
+        <v>2184920.9</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.325795126999368</v>
       </c>
       <c r="AF2">
-        <v>2174899.8</v>
+        <v>2184922.225795127</v>
       </c>
       <c r="AG2">
-        <v>1339675.1</v>
+        <v>1343659.225795127</v>
       </c>
       <c r="AH2">
-        <v>0.8669856736274805</v>
+        <v>0.8657187547960652</v>
       </c>
       <c r="AI2">
-        <v>0.8245935845938348</v>
+        <v>0.823020520747281</v>
       </c>
       <c r="AJ2">
-        <v>0.8005938620076102</v>
+        <v>0.7985795498088278</v>
       </c>
       <c r="AK2">
-        <v>0.7433072254555914</v>
+        <v>0.740921536901633</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>3256215.946348733</v>
+      </c>
+      <c r="AP2">
+        <v>2002472.765715539</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc (LSE:HSBA)</t>
+          <t>Bank of Georgia Group PLC (LSE:BGEO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0195</v>
+        <v>0.263</v>
       </c>
       <c r="E3">
-        <v>0.103</v>
-      </c>
-      <c r="F3">
-        <v>0.169</v>
+        <v>0.382</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +731,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.0003594057515056026</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.0003143405983062657</v>
       </c>
       <c r="K3">
-        <v>23600</v>
+        <v>842.6</v>
       </c>
       <c r="L3">
-        <v>0.4071071243746766</v>
+        <v>0.7461919943322706</v>
       </c>
       <c r="M3">
-        <v>10780.652</v>
+        <v>179.31</v>
       </c>
       <c r="N3">
-        <v>0.0620464180432503</v>
+        <v>0.07080075811419095</v>
       </c>
       <c r="O3">
-        <v>0.4568072881355932</v>
+        <v>0.212805601708996</v>
       </c>
       <c r="P3">
-        <v>10780.652</v>
+        <v>179.31</v>
       </c>
       <c r="Q3">
-        <v>0.0620464180432503</v>
+        <v>0.07080075811419095</v>
       </c>
       <c r="R3">
-        <v>0.4568072881355932</v>
+        <v>0.212805601708996</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,61 +767,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>252310</v>
+        <v>1250.4</v>
       </c>
       <c r="V3">
-        <v>1.452132184258659</v>
-      </c>
-      <c r="W3">
-        <v>0.1291593695271454</v>
+        <v>0.4937218668561953</v>
       </c>
       <c r="X3">
-        <v>0.1287580685930172</v>
-      </c>
-      <c r="Y3">
-        <v>0.0004013009341281848</v>
+        <v>0.08390863023983756</v>
       </c>
       <c r="Z3">
-        <v>0.09954118673287864</v>
+        <v>851.7153042760721</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.2677286983327437</v>
       </c>
       <c r="AB3">
-        <v>0.06203848417014039</v>
+        <v>0.06332840255846163</v>
       </c>
       <c r="AC3">
-        <v>-0.06203848417014039</v>
+        <v>0.204400295774282</v>
       </c>
       <c r="AD3">
-        <v>719546</v>
+        <v>2994</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.325795126999368</v>
       </c>
       <c r="AF3">
-        <v>719546</v>
+        <v>2995.325795126999</v>
       </c>
       <c r="AG3">
-        <v>467236</v>
+        <v>1744.925795126999</v>
       </c>
       <c r="AH3">
-        <v>0.8054943404066776</v>
+        <v>0.5418534738233013</v>
       </c>
       <c r="AI3">
-        <v>0.7824800912599462</v>
+        <v>0.5559123726910683</v>
       </c>
       <c r="AJ3">
-        <v>0.7289316451462228</v>
+        <v>0.4079287603863982</v>
       </c>
       <c r="AK3">
-        <v>0.7002297451821701</v>
+        <v>0.4217113171641289</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>4461.997019374068</v>
+      </c>
+      <c r="AP3">
+        <v>2600.485536701936</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barclays PLC (LSE:BARC)</t>
+          <t>Close Brothers Group plc (LSE:CBG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0392</v>
+        <v>0.0244</v>
       </c>
       <c r="E4">
-        <v>0.148</v>
+        <v>-0.13</v>
       </c>
       <c r="F4">
-        <v>0.164</v>
+        <v>0.491</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +862,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>6999.1</v>
+        <v>128.9</v>
       </c>
       <c r="L4">
-        <v>0.2212818291611076</v>
+        <v>0.1083102260314259</v>
       </c>
       <c r="M4">
-        <v>1582.416</v>
+        <v>90.69</v>
       </c>
       <c r="N4">
-        <v>0.03276691701298944</v>
+        <v>0.20583295506128</v>
       </c>
       <c r="O4">
-        <v>0.2260884970924833</v>
+        <v>0.7035686578743211</v>
       </c>
       <c r="P4">
-        <v>1582.416</v>
+        <v>86.2</v>
       </c>
       <c r="Q4">
-        <v>0.03276691701298944</v>
+        <v>0.1956423059464367</v>
       </c>
       <c r="R4">
-        <v>0.2260884970924833</v>
+        <v>0.6687354538401862</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>4.489999999999995</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.04950931745506666</v>
       </c>
       <c r="U4">
-        <v>288246.9</v>
+        <v>2368.2</v>
       </c>
       <c r="V4">
-        <v>5.968697391552832</v>
+        <v>5.37494325919201</v>
       </c>
       <c r="W4">
-        <v>0.08395638984284942</v>
+        <v>0.06092546202202582</v>
       </c>
       <c r="X4">
-        <v>0.3608937229360646</v>
+        <v>0.1782307151256188</v>
       </c>
       <c r="Y4">
-        <v>-0.2769373330932152</v>
+        <v>-0.117305253103593</v>
       </c>
       <c r="Z4">
-        <v>0.04662886505686236</v>
+        <v>0.3786871161739904</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06210612775214323</v>
+        <v>0.0616588922926672</v>
       </c>
       <c r="AC4">
-        <v>-0.06210612775214323</v>
+        <v>-0.0616588922926672</v>
       </c>
       <c r="AD4">
-        <v>939800.3</v>
+        <v>3264.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>939800.3</v>
+        <v>3264.9</v>
       </c>
       <c r="AG4">
-        <v>651553.4</v>
+        <v>896.7000000000003</v>
       </c>
       <c r="AH4">
-        <v>0.9511249645023436</v>
+        <v>0.8810956686007286</v>
       </c>
       <c r="AI4">
-        <v>0.9073105087241479</v>
+        <v>0.5798287987497336</v>
       </c>
       <c r="AJ4">
-        <v>0.930994725271899</v>
+        <v>0.6705301727361102</v>
       </c>
       <c r="AK4">
-        <v>0.8715710536383605</v>
+        <v>0.2748421504321707</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Standard Chartered PLC (LSE:STAN)</t>
+          <t>Secure Trust Bank PLC (LSE:STB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +966,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0529</v>
+        <v>0.0254</v>
       </c>
       <c r="E5">
-        <v>0.364</v>
-      </c>
-      <c r="F5">
-        <v>0.11</v>
+        <v>-0.0295</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4464</v>
+        <v>32.9</v>
       </c>
       <c r="L5">
-        <v>0.2417677642980936</v>
+        <v>0.181367144432194</v>
       </c>
       <c r="M5">
-        <v>719.64</v>
+        <v>9.73</v>
       </c>
       <c r="N5">
-        <v>0.02423928054161474</v>
+        <v>0.1126157407407407</v>
       </c>
       <c r="O5">
-        <v>0.1612096774193548</v>
+        <v>0.2957446808510639</v>
       </c>
       <c r="P5">
-        <v>719.64</v>
+        <v>7.71</v>
       </c>
       <c r="Q5">
-        <v>0.02423928054161474</v>
+        <v>0.0892361111111111</v>
       </c>
       <c r="R5">
-        <v>0.1612096774193548</v>
+        <v>0.2343465045592705</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.2076053442959918</v>
       </c>
       <c r="U5">
-        <v>64905</v>
+        <v>548.4</v>
       </c>
       <c r="V5">
-        <v>2.18616322543703</v>
+        <v>6.347222222222221</v>
       </c>
       <c r="W5">
-        <v>0.09603304362791498</v>
+        <v>0.07770429853566367</v>
       </c>
       <c r="X5">
-        <v>0.1415848784993639</v>
+        <v>0.168214792352272</v>
       </c>
       <c r="Y5">
-        <v>-0.04555183487144895</v>
+        <v>-0.09051049381660838</v>
       </c>
       <c r="Z5">
-        <v>0.1574325130881124</v>
+        <v>0.2922036082474227</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06259031723364959</v>
+        <v>0.06170882963581631</v>
       </c>
       <c r="AC5">
-        <v>-0.06259031723364959</v>
+        <v>-0.06170882963581631</v>
       </c>
       <c r="AD5">
-        <v>148080</v>
+        <v>583.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>148080</v>
+        <v>583.1</v>
       </c>
       <c r="AG5">
-        <v>83175</v>
+        <v>34.70000000000005</v>
       </c>
       <c r="AH5">
-        <v>0.8329911289369912</v>
+        <v>0.8709484690067215</v>
       </c>
       <c r="AI5">
-        <v>0.7373914429129153</v>
+        <v>0.5648004649360713</v>
       </c>
       <c r="AJ5">
-        <v>0.7369488942444004</v>
+        <v>0.2865400495458301</v>
       </c>
       <c r="AK5">
-        <v>0.6119813701613556</v>
+        <v>0.07169421487603314</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
+          <t>HSBC Holdings plc (LSE:HSBA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0186</v>
+        <v>0.0195</v>
       </c>
       <c r="E6">
-        <v>0.133</v>
+        <v>0.103</v>
       </c>
       <c r="F6">
-        <v>0.03759999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1109,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>6645.2</v>
+        <v>23600</v>
       </c>
       <c r="L6">
-        <v>0.2671469404656137</v>
+        <v>0.4071071243746766</v>
       </c>
       <c r="M6">
-        <v>2360.67</v>
+        <v>10780.652</v>
       </c>
       <c r="N6">
-        <v>0.05686744491927596</v>
+        <v>0.0620464180432503</v>
       </c>
       <c r="O6">
-        <v>0.3552443869259014</v>
+        <v>0.4568072881355932</v>
       </c>
       <c r="P6">
-        <v>2360.67</v>
+        <v>10780.652</v>
       </c>
       <c r="Q6">
-        <v>0.05686744491927596</v>
+        <v>0.0620464180432503</v>
       </c>
       <c r="R6">
-        <v>0.3552443869259014</v>
+        <v>0.4568072881355932</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1139,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>79151.60000000001</v>
+        <v>252310</v>
       </c>
       <c r="V6">
-        <v>1.906725316656951</v>
+        <v>1.452132184258659</v>
       </c>
       <c r="W6">
-        <v>0.1215780335505023</v>
+        <v>0.1291593695271454</v>
       </c>
       <c r="X6">
-        <v>0.1344123212962882</v>
+        <v>0.1287193263571053</v>
       </c>
       <c r="Y6">
-        <v>-0.01283428774578595</v>
+        <v>0.0004400431700400664</v>
       </c>
       <c r="Z6">
-        <v>0.170810458189559</v>
+        <v>0.09954118673287864</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06264907291991287</v>
+        <v>0.06203094858599024</v>
       </c>
       <c r="AC6">
-        <v>-0.06264907291991287</v>
+        <v>-0.06203094858599024</v>
       </c>
       <c r="AD6">
-        <v>187399.8</v>
+        <v>719546</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>187399.8</v>
+        <v>719546</v>
       </c>
       <c r="AG6">
-        <v>108248.2</v>
+        <v>467236</v>
       </c>
       <c r="AH6">
-        <v>0.8186557605643402</v>
+        <v>0.8054943404066776</v>
       </c>
       <c r="AI6">
-        <v>0.7507463404081436</v>
+        <v>0.7824800912599462</v>
       </c>
       <c r="AJ6">
-        <v>0.7228111645299145</v>
+        <v>0.7289316451462228</v>
       </c>
       <c r="AK6">
-        <v>0.6350119437026887</v>
+        <v>0.7002297451821701</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,120 +1204,617 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Barclays PLC (LSE:BARC)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0392</v>
+      </c>
+      <c r="E7">
+        <v>0.148</v>
+      </c>
+      <c r="F7">
+        <v>0.164</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>6999.1</v>
+      </c>
+      <c r="L7">
+        <v>0.2212818291611076</v>
+      </c>
+      <c r="M7">
+        <v>1582.416</v>
+      </c>
+      <c r="N7">
+        <v>0.03276691701298944</v>
+      </c>
+      <c r="O7">
+        <v>0.2260884970924833</v>
+      </c>
+      <c r="P7">
+        <v>1582.416</v>
+      </c>
+      <c r="Q7">
+        <v>0.03276691701298944</v>
+      </c>
+      <c r="R7">
+        <v>0.2260884970924833</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>288246.9</v>
+      </c>
+      <c r="V7">
+        <v>5.968697391552832</v>
+      </c>
+      <c r="W7">
+        <v>0.08395638984284942</v>
+      </c>
+      <c r="X7">
+        <v>0.3607465710609623</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2767901812181128</v>
+      </c>
+      <c r="Z7">
+        <v>0.04662886505686236</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06209893569902405</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06209893569902405</v>
+      </c>
+      <c r="AD7">
+        <v>939800.3</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>939800.3</v>
+      </c>
+      <c r="AG7">
+        <v>651553.4</v>
+      </c>
+      <c r="AH7">
+        <v>0.9511249645023436</v>
+      </c>
+      <c r="AI7">
+        <v>0.9073105087241479</v>
+      </c>
+      <c r="AJ7">
+        <v>0.930994725271899</v>
+      </c>
+      <c r="AK7">
+        <v>0.8715710536383605</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Standard Chartered PLC (LSE:STAN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0529</v>
+      </c>
+      <c r="E8">
+        <v>0.364</v>
+      </c>
+      <c r="F8">
+        <v>0.11</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>4464</v>
+      </c>
+      <c r="L8">
+        <v>0.2417677642980936</v>
+      </c>
+      <c r="M8">
+        <v>719.64</v>
+      </c>
+      <c r="N8">
+        <v>0.02423928054161474</v>
+      </c>
+      <c r="O8">
+        <v>0.1612096774193548</v>
+      </c>
+      <c r="P8">
+        <v>719.64</v>
+      </c>
+      <c r="Q8">
+        <v>0.02423928054161474</v>
+      </c>
+      <c r="R8">
+        <v>0.1612096774193548</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>64905</v>
+      </c>
+      <c r="V8">
+        <v>2.18616322543703</v>
+      </c>
+      <c r="W8">
+        <v>0.09603304362791498</v>
+      </c>
+      <c r="X8">
+        <v>0.141540146016767</v>
+      </c>
+      <c r="Y8">
+        <v>-0.04550710238885203</v>
+      </c>
+      <c r="Z8">
+        <v>0.1574325130881124</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06258284651223123</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06258284651223123</v>
+      </c>
+      <c r="AD8">
+        <v>148080</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>148080</v>
+      </c>
+      <c r="AG8">
+        <v>83175</v>
+      </c>
+      <c r="AH8">
+        <v>0.8329911289369912</v>
+      </c>
+      <c r="AI8">
+        <v>0.7373914429129153</v>
+      </c>
+      <c r="AJ8">
+        <v>0.7369488942444004</v>
+      </c>
+      <c r="AK8">
+        <v>0.6119813701613556</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lloyds Banking Group plc (LSE:LLOY)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0186</v>
+      </c>
+      <c r="E9">
+        <v>0.133</v>
+      </c>
+      <c r="F9">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>6645.2</v>
+      </c>
+      <c r="L9">
+        <v>0.2671469404656137</v>
+      </c>
+      <c r="M9">
+        <v>2360.67</v>
+      </c>
+      <c r="N9">
+        <v>0.05686744491927596</v>
+      </c>
+      <c r="O9">
+        <v>0.3552443869259014</v>
+      </c>
+      <c r="P9">
+        <v>2360.67</v>
+      </c>
+      <c r="Q9">
+        <v>0.05686744491927596</v>
+      </c>
+      <c r="R9">
+        <v>0.3552443869259014</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>79151.60000000001</v>
+      </c>
+      <c r="V9">
+        <v>1.906725316656951</v>
+      </c>
+      <c r="W9">
+        <v>0.1215780335505023</v>
+      </c>
+      <c r="X9">
+        <v>0.134370938468619</v>
+      </c>
+      <c r="Y9">
+        <v>-0.01279290491811667</v>
+      </c>
+      <c r="Z9">
+        <v>0.170810458189559</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06264156838250348</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06264156838250348</v>
+      </c>
+      <c r="AD9">
+        <v>187399.8</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>187399.8</v>
+      </c>
+      <c r="AG9">
+        <v>108248.2</v>
+      </c>
+      <c r="AH9">
+        <v>0.8186557605643402</v>
+      </c>
+      <c r="AI9">
+        <v>0.7507463404081436</v>
+      </c>
+      <c r="AJ9">
+        <v>0.7228111645299145</v>
+      </c>
+      <c r="AK9">
+        <v>0.6350119437026887</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>NatWest Group plc (LSE:NWG)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D10">
         <v>0.0283</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>0.138</v>
       </c>
-      <c r="F7">
+      <c r="F10">
         <v>0.08400000000000001</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>6382.5</v>
       </c>
-      <c r="L7">
+      <c r="L10">
         <v>0.3403110653749153</v>
       </c>
-      <c r="M7">
+      <c r="M10">
         <v>2529.9855</v>
       </c>
-      <c r="N7">
+      <c r="N10">
         <v>0.06257492338856281</v>
       </c>
-      <c r="O7">
+      <c r="O10">
         <v>0.3963941245593419</v>
       </c>
-      <c r="P7">
+      <c r="P10">
         <v>2529.9855</v>
       </c>
-      <c r="Q7">
+      <c r="Q10">
         <v>0.06257492338856281</v>
       </c>
-      <c r="R7">
+      <c r="R10">
         <v>0.3963941245593419</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
         <v>150611.2</v>
       </c>
-      <c r="V7">
+      <c r="V10">
         <v>3.725113958739887</v>
       </c>
-      <c r="W7">
+      <c r="W10">
         <v>0.1476623881398125</v>
       </c>
-      <c r="X7">
-        <v>0.1334947101023821</v>
-      </c>
-      <c r="Y7">
-        <v>0.01416767803743041</v>
-      </c>
-      <c r="Z7">
+      <c r="X10">
+        <v>0.1334537558081871</v>
+      </c>
+      <c r="Y10">
+        <v>0.01420863233162545</v>
+      </c>
+      <c r="Z10">
         <v>0.2490300324783102</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.06265732558667859</v>
-      </c>
-      <c r="AC7">
-        <v>-0.06265732558667859</v>
-      </c>
-      <c r="AD7">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06264981629956544</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06264981629956544</v>
+      </c>
+      <c r="AD10">
         <v>180073.7</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>180073.7</v>
       </c>
-      <c r="AG7">
+      <c r="AG10">
         <v>29462.5</v>
       </c>
-      <c r="AH7">
+      <c r="AH10">
         <v>0.8166422530101359</v>
       </c>
-      <c r="AI7">
+      <c r="AI10">
         <v>0.7770921547541165</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ10">
         <v>0.4215323819852405</v>
       </c>
-      <c r="AK7">
+      <c r="AK10">
         <v>0.3632126179169687</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TBC Bank Group PLC (LSE:TBCG)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.201</v>
+      </c>
+      <c r="E11">
+        <v>0.196</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>456.1</v>
+      </c>
+      <c r="L11">
+        <v>0.4957608695652174</v>
+      </c>
+      <c r="M11">
+        <v>146.52</v>
+      </c>
+      <c r="N11">
+        <v>0.06764230644937907</v>
+      </c>
+      <c r="O11">
+        <v>0.3212453409340057</v>
+      </c>
+      <c r="P11">
+        <v>146.52</v>
+      </c>
+      <c r="Q11">
+        <v>0.06764230644937907</v>
+      </c>
+      <c r="R11">
+        <v>0.3212453409340057</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1871.3</v>
+      </c>
+      <c r="V11">
+        <v>0.8639028669036517</v>
+      </c>
+      <c r="W11">
+        <v>0.280383598696748</v>
+      </c>
+      <c r="X11">
+        <v>0.08822460384764649</v>
+      </c>
+      <c r="Y11">
+        <v>0.1921589948491015</v>
+      </c>
+      <c r="Z11">
+        <v>0.3383099213061705</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0630680443048499</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0630680443048499</v>
+      </c>
+      <c r="AD11">
+        <v>3179.1</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>3179.1</v>
+      </c>
+      <c r="AG11">
+        <v>1307.8</v>
+      </c>
+      <c r="AH11">
+        <v>0.5947579136421463</v>
+      </c>
+      <c r="AI11">
+        <v>0.615210449927431</v>
+      </c>
+      <c r="AJ11">
+        <v>0.376464492357293</v>
+      </c>
+      <c r="AK11">
+        <v>0.3967599053455494</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
         <v>0</v>
       </c>
     </row>
